--- a/grupos/4AEV - Estadisticos 20222.xlsx
+++ b/grupos/4AEV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="153">
   <si>
     <t>Materia</t>
   </si>
@@ -979,7 +979,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -1042,7 +1042,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>5</v>
@@ -1068,7 +1068,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>7</v>
@@ -1131,7 +1131,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1157,7 +1157,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1220,7 +1220,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -1246,7 +1246,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1309,7 +1309,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1335,7 +1335,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>9</v>
@@ -1398,7 +1398,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1424,7 +1424,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -1487,7 +1487,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1513,7 +1513,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -1576,7 +1576,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1602,7 +1602,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1665,7 +1665,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1691,7 +1691,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -1754,7 +1754,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1780,7 +1780,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1843,7 +1843,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1869,7 +1869,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -1932,7 +1932,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1958,7 +1958,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -2021,7 +2021,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -2047,7 +2047,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -2110,7 +2110,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -2136,7 +2136,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -2199,7 +2199,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2225,7 +2225,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -2288,7 +2288,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -2314,7 +2314,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C19">
         <v>9</v>
@@ -2377,7 +2377,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2403,7 +2403,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C20">
         <v>6</v>
@@ -2466,7 +2466,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2492,7 +2492,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -2555,7 +2555,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2581,7 +2581,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>7</v>
@@ -2644,7 +2644,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2670,7 +2670,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>8</v>
@@ -2733,7 +2733,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2762,7 +2762,7 @@
         <v>-1</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -2798,7 +2798,7 @@
         <v>-1</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB24">
         <v>5</v>
@@ -2812,7 +2812,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C25">
         <v>6</v>
@@ -2875,7 +2875,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2901,7 +2901,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -2978,7 +2978,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>6</v>
@@ -3032,7 +3032,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -3055,7 +3055,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -3118,7 +3118,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -3144,7 +3144,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C29">
         <v>8</v>
@@ -3207,7 +3207,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -3233,7 +3233,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C30">
         <v>9</v>
@@ -3296,7 +3296,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -3322,7 +3322,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C31">
         <v>7</v>
@@ -3385,7 +3385,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3411,7 +3411,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>6</v>
@@ -3474,7 +3474,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -3500,7 +3500,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C33">
         <v>7</v>
@@ -3563,7 +3563,7 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>7</v>
@@ -3589,7 +3589,7 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C34">
         <v>6</v>
@@ -3652,7 +3652,7 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X34">
         <v>6</v>
@@ -3678,7 +3678,7 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C35">
         <v>10</v>
@@ -3741,7 +3741,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3767,7 +3767,7 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="C36">
         <v>6</v>
@@ -3830,7 +3830,7 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X36">
         <v>6</v>
@@ -3978,7 +3978,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>95</v>
@@ -4046,7 +4046,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -4114,7 +4114,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C6">
         <v>95</v>
@@ -4182,7 +4182,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>85</v>
@@ -4250,7 +4250,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -4318,7 +4318,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -4386,7 +4386,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C10">
         <v>95</v>
@@ -4454,7 +4454,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4522,7 +4522,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C12">
         <v>80</v>
@@ -4590,7 +4590,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -4658,7 +4658,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C14">
         <v>95</v>
@@ -4726,7 +4726,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C15">
         <v>90</v>
@@ -4794,7 +4794,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C16">
         <v>95</v>
@@ -4862,7 +4862,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C17">
         <v>95</v>
@@ -4930,7 +4930,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C18">
         <v>80</v>
@@ -4998,7 +4998,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -5066,7 +5066,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -5134,7 +5134,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -5202,7 +5202,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -5270,7 +5270,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -5341,7 +5341,7 @@
         <v>93.3</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="G24">
         <v>66.7</v>
@@ -5379,7 +5379,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>95</v>
@@ -5447,7 +5447,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="C26">
         <v>90</v>
@@ -5506,7 +5506,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="C27">
         <v>90</v>
@@ -5565,7 +5565,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -5633,7 +5633,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -5701,7 +5701,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -5769,7 +5769,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -5837,7 +5837,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -5905,7 +5905,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -5973,7 +5973,7 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -6041,7 +6041,7 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -6109,7 +6109,7 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -6253,13 +6253,13 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -6274,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3">
         <v>100</v>
@@ -6282,121 +6282,124 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>33</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>57.58</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>42.42</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
       </c>
       <c r="I4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>57.58</v>
+        <v>58.06</v>
       </c>
       <c r="G5">
-        <v>42.42</v>
+        <v>29.03</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>9</v>
       </c>
       <c r="F6">
-        <v>58.06</v>
+        <v>71.88</v>
       </c>
       <c r="G6">
-        <v>29.03</v>
+        <v>28.13</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>12.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
       </c>
       <c r="C7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>9</v>
       </c>
       <c r="F7">
-        <v>71.88</v>
+        <v>72.73</v>
       </c>
       <c r="G7">
-        <v>28.13</v>
+        <v>27.27</v>
       </c>
       <c r="H7">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6407,13 +6410,13 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>58</v>
       </c>
       <c r="C8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8">
         <v>24</v>
@@ -6422,19 +6425,19 @@
         <v>8</v>
       </c>
       <c r="F8">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="G8">
-        <v>24.24</v>
+        <v>25</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6444,7 +6447,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6505,30 +6508,30 @@
         <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920001</v>
+        <v>21330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6545,27 +6548,27 @@
         <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920003</v>
+        <v>21330051920005</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>58</v>
@@ -6573,16 +6576,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920003</v>
+        <v>21330051920005</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -6593,16 +6596,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920005</v>
+        <v>20330051920005</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -6613,79 +6616,79 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920005</v>
+        <v>20330051920005</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920005</v>
+        <v>21330051920008</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920005</v>
+        <v>21330051920008</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920005</v>
+        <v>20330051920049</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>58</v>
@@ -6693,16 +6696,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920005</v>
+        <v>20330051920049</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -6713,16 +6716,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920008</v>
+        <v>21330051920010</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -6733,139 +6736,139 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920008</v>
+        <v>21330051920010</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920008</v>
+        <v>21330051920355</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920049</v>
+        <v>21330051920355</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920049</v>
+        <v>21330051920355</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920049</v>
+        <v>20330051920078</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920010</v>
+        <v>20330051920078</v>
       </c>
       <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" t="s">
         <v>72</v>
       </c>
-      <c r="C20" t="s">
-        <v>101</v>
-      </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920010</v>
+        <v>21330051920011</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
         <v>58</v>
@@ -6873,16 +6876,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920010</v>
+        <v>21330051920011</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
@@ -6893,16 +6896,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920355</v>
+        <v>21330051920195</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -6913,56 +6916,56 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920355</v>
+        <v>21330051920195</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920355</v>
+        <v>21330051920012</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920355</v>
+        <v>21330051920012</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E26" t="s">
         <v>11</v>
@@ -6973,16 +6976,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920078</v>
+        <v>20330051920018</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -6993,79 +6996,79 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920078</v>
+        <v>20330051920018</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920078</v>
+        <v>21330051920013</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920011</v>
+        <v>21330051920013</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920011</v>
+        <v>20330051920019</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F31" t="s">
         <v>58</v>
@@ -7073,59 +7076,59 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920011</v>
+        <v>20330051920019</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E32" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920195</v>
+        <v>20330051920019</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="D33" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920195</v>
+        <v>20330051920391</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E34" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s">
         <v>58</v>
@@ -7133,16 +7136,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920195</v>
+        <v>20330051920391</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="D35" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E35" t="s">
         <v>11</v>
@@ -7153,16 +7156,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920012</v>
+        <v>21330051920015</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D36" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
@@ -7173,79 +7176,79 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920012</v>
+        <v>21330051920015</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D37" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920012</v>
+        <v>20330051920088</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="D38" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E38" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920018</v>
+        <v>20330051920088</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D39" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E39" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920018</v>
+        <v>21330051920016</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D40" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E40" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F40" t="s">
         <v>58</v>
@@ -7253,16 +7256,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920018</v>
+        <v>21330051920016</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D41" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E41" t="s">
         <v>11</v>
@@ -7273,99 +7276,99 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920013</v>
+        <v>20330051920089</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920013</v>
+        <v>20330051920089</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E43" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920013</v>
+        <v>20330051920022</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C44" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E44" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920019</v>
+        <v>20330051920022</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D45" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E45" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920019</v>
+        <v>21330051920379</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D46" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E46" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F46" t="s">
         <v>58</v>
@@ -7373,16 +7376,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920019</v>
+        <v>21330051920379</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D47" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -7393,16 +7396,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>20330051920019</v>
+        <v>21330051920379</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C48" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D48" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E48" t="s">
         <v>11</v>
@@ -7413,16 +7416,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>20330051920391</v>
+        <v>20330051920366</v>
       </c>
       <c r="B49" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C49" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="D49" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E49" t="s">
         <v>7</v>
@@ -7433,79 +7436,79 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>20330051920391</v>
+        <v>20330051920366</v>
       </c>
       <c r="B50" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="D50" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E50" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>20330051920391</v>
+        <v>20330051920367</v>
       </c>
       <c r="B51" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="D51" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E51" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>21330051920015</v>
+        <v>20330051920367</v>
       </c>
       <c r="B52" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
         <v>74</v>
       </c>
       <c r="D52" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E52" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>21330051920015</v>
+        <v>21330051920018</v>
       </c>
       <c r="B53" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C53" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="D53" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E53" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F53" t="s">
         <v>58</v>
@@ -7513,16 +7516,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>21330051920015</v>
+        <v>21330051920018</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="D54" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E54" t="s">
         <v>11</v>
@@ -7533,16 +7536,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>20330051920088</v>
+        <v>21330051920019</v>
       </c>
       <c r="B55" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C55" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D55" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E55" t="s">
         <v>7</v>
@@ -7553,79 +7556,79 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>20330051920088</v>
+        <v>21330051920019</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C56" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D56" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E56" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F56" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>20330051920088</v>
+        <v>21330051920021</v>
       </c>
       <c r="B57" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C57" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D57" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E57" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>21330051920016</v>
+        <v>21330051920021</v>
       </c>
       <c r="B58" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C58" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D58" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E58" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>21330051920016</v>
+        <v>21330051920022</v>
       </c>
       <c r="B59" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C59" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D59" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="E59" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F59" t="s">
         <v>58</v>
@@ -7633,16 +7636,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>21330051920016</v>
+        <v>21330051920022</v>
       </c>
       <c r="B60" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C60" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D60" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="E60" t="s">
         <v>11</v>
@@ -7653,36 +7656,36 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>20330051920089</v>
+        <v>21330051920023</v>
       </c>
       <c r="B61" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C61" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="D61" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F61" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>20330051920089</v>
+        <v>21330051920023</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C62" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="D62" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E62" t="s">
         <v>11</v>
@@ -7693,19 +7696,19 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>20330051920089</v>
+        <v>21330051920025</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C63" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D63" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E63" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F63" t="s">
         <v>58</v>
@@ -7713,39 +7716,39 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>20330051920022</v>
+        <v>21330051920025</v>
       </c>
       <c r="B64" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C64" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D64" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E64" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F64" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>20330051920022</v>
+        <v>21330051920027</v>
       </c>
       <c r="B65" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C65" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D65" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E65" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F65" t="s">
         <v>58</v>
@@ -7753,16 +7756,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>20330051920022</v>
+        <v>21330051920027</v>
       </c>
       <c r="B66" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C66" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D66" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E66" t="s">
         <v>11</v>
@@ -7773,16 +7776,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>21330051920379</v>
+        <v>21330051920028</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D67" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E67" t="s">
         <v>7</v>
@@ -7793,721 +7796,61 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>21330051920379</v>
+        <v>21330051920028</v>
       </c>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D68" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E68" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F68" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>21330051920379</v>
+        <v>21330051920393</v>
       </c>
       <c r="B69" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D69" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E69" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F69" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>21330051920379</v>
+        <v>21330051920393</v>
       </c>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D70" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E70" t="s">
         <v>11</v>
       </c>
       <c r="F70" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>20330051920366</v>
-      </c>
-      <c r="B71" t="s">
-        <v>87</v>
-      </c>
-      <c r="C71" t="s">
-        <v>74</v>
-      </c>
-      <c r="D71" t="s">
-        <v>143</v>
-      </c>
-      <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>20330051920366</v>
-      </c>
-      <c r="B72" t="s">
-        <v>87</v>
-      </c>
-      <c r="C72" t="s">
-        <v>74</v>
-      </c>
-      <c r="D72" t="s">
-        <v>143</v>
-      </c>
-      <c r="E72" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920366</v>
-      </c>
-      <c r="B73" t="s">
-        <v>87</v>
-      </c>
-      <c r="C73" t="s">
-        <v>74</v>
-      </c>
-      <c r="D73" t="s">
-        <v>143</v>
-      </c>
-      <c r="E73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>20330051920367</v>
-      </c>
-      <c r="B74" t="s">
-        <v>87</v>
-      </c>
-      <c r="C74" t="s">
-        <v>74</v>
-      </c>
-      <c r="D74" t="s">
-        <v>144</v>
-      </c>
-      <c r="E74" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>20330051920367</v>
-      </c>
-      <c r="B75" t="s">
-        <v>87</v>
-      </c>
-      <c r="C75" t="s">
-        <v>74</v>
-      </c>
-      <c r="D75" t="s">
-        <v>144</v>
-      </c>
-      <c r="E75" t="s">
-        <v>5</v>
-      </c>
-      <c r="F75" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>20330051920367</v>
-      </c>
-      <c r="B76" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" t="s">
-        <v>74</v>
-      </c>
-      <c r="D76" t="s">
-        <v>144</v>
-      </c>
-      <c r="E76" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920018</v>
-      </c>
-      <c r="B77" t="s">
-        <v>88</v>
-      </c>
-      <c r="C77" t="s">
-        <v>113</v>
-      </c>
-      <c r="D77" t="s">
-        <v>145</v>
-      </c>
-      <c r="E77" t="s">
-        <v>7</v>
-      </c>
-      <c r="F77" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920018</v>
-      </c>
-      <c r="B78" t="s">
-        <v>88</v>
-      </c>
-      <c r="C78" t="s">
-        <v>113</v>
-      </c>
-      <c r="D78" t="s">
-        <v>145</v>
-      </c>
-      <c r="E78" t="s">
-        <v>5</v>
-      </c>
-      <c r="F78" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920018</v>
-      </c>
-      <c r="B79" t="s">
-        <v>88</v>
-      </c>
-      <c r="C79" t="s">
-        <v>113</v>
-      </c>
-      <c r="D79" t="s">
-        <v>145</v>
-      </c>
-      <c r="E79" t="s">
-        <v>11</v>
-      </c>
-      <c r="F79" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920019</v>
-      </c>
-      <c r="B80" t="s">
-        <v>89</v>
-      </c>
-      <c r="C80" t="s">
-        <v>114</v>
-      </c>
-      <c r="D80" t="s">
-        <v>146</v>
-      </c>
-      <c r="E80" t="s">
-        <v>7</v>
-      </c>
-      <c r="F80" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920019</v>
-      </c>
-      <c r="B81" t="s">
-        <v>89</v>
-      </c>
-      <c r="C81" t="s">
-        <v>114</v>
-      </c>
-      <c r="D81" t="s">
-        <v>146</v>
-      </c>
-      <c r="E81" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920019</v>
-      </c>
-      <c r="B82" t="s">
-        <v>89</v>
-      </c>
-      <c r="C82" t="s">
-        <v>114</v>
-      </c>
-      <c r="D82" t="s">
-        <v>146</v>
-      </c>
-      <c r="E82" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920021</v>
-      </c>
-      <c r="B83" t="s">
-        <v>90</v>
-      </c>
-      <c r="C83" t="s">
-        <v>115</v>
-      </c>
-      <c r="D83" t="s">
-        <v>147</v>
-      </c>
-      <c r="E83" t="s">
-        <v>7</v>
-      </c>
-      <c r="F83" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>21330051920021</v>
-      </c>
-      <c r="B84" t="s">
-        <v>90</v>
-      </c>
-      <c r="C84" t="s">
-        <v>115</v>
-      </c>
-      <c r="D84" t="s">
-        <v>147</v>
-      </c>
-      <c r="E84" t="s">
-        <v>5</v>
-      </c>
-      <c r="F84" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>21330051920021</v>
-      </c>
-      <c r="B85" t="s">
-        <v>90</v>
-      </c>
-      <c r="C85" t="s">
-        <v>115</v>
-      </c>
-      <c r="D85" t="s">
-        <v>147</v>
-      </c>
-      <c r="E85" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>21330051920022</v>
-      </c>
-      <c r="B86" t="s">
-        <v>91</v>
-      </c>
-      <c r="C86" t="s">
-        <v>116</v>
-      </c>
-      <c r="D86" t="s">
-        <v>148</v>
-      </c>
-      <c r="E86" t="s">
-        <v>7</v>
-      </c>
-      <c r="F86" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>21330051920022</v>
-      </c>
-      <c r="B87" t="s">
-        <v>91</v>
-      </c>
-      <c r="C87" t="s">
-        <v>116</v>
-      </c>
-      <c r="D87" t="s">
-        <v>148</v>
-      </c>
-      <c r="E87" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>21330051920022</v>
-      </c>
-      <c r="B88" t="s">
-        <v>91</v>
-      </c>
-      <c r="C88" t="s">
-        <v>116</v>
-      </c>
-      <c r="D88" t="s">
-        <v>148</v>
-      </c>
-      <c r="E88" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>21330051920023</v>
-      </c>
-      <c r="B89" t="s">
-        <v>92</v>
-      </c>
-      <c r="C89" t="s">
-        <v>74</v>
-      </c>
-      <c r="D89" t="s">
-        <v>149</v>
-      </c>
-      <c r="E89" t="s">
-        <v>7</v>
-      </c>
-      <c r="F89" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>21330051920023</v>
-      </c>
-      <c r="B90" t="s">
-        <v>92</v>
-      </c>
-      <c r="C90" t="s">
-        <v>74</v>
-      </c>
-      <c r="D90" t="s">
-        <v>149</v>
-      </c>
-      <c r="E90" t="s">
-        <v>5</v>
-      </c>
-      <c r="F90" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>21330051920023</v>
-      </c>
-      <c r="B91" t="s">
-        <v>92</v>
-      </c>
-      <c r="C91" t="s">
-        <v>74</v>
-      </c>
-      <c r="D91" t="s">
-        <v>149</v>
-      </c>
-      <c r="E91" t="s">
-        <v>11</v>
-      </c>
-      <c r="F91" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>21330051920025</v>
-      </c>
-      <c r="B92" t="s">
-        <v>93</v>
-      </c>
-      <c r="C92" t="s">
-        <v>117</v>
-      </c>
-      <c r="D92" t="s">
-        <v>150</v>
-      </c>
-      <c r="E92" t="s">
-        <v>7</v>
-      </c>
-      <c r="F92" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>21330051920025</v>
-      </c>
-      <c r="B93" t="s">
-        <v>93</v>
-      </c>
-      <c r="C93" t="s">
-        <v>117</v>
-      </c>
-      <c r="D93" t="s">
-        <v>150</v>
-      </c>
-      <c r="E93" t="s">
-        <v>5</v>
-      </c>
-      <c r="F93" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>21330051920025</v>
-      </c>
-      <c r="B94" t="s">
-        <v>93</v>
-      </c>
-      <c r="C94" t="s">
-        <v>117</v>
-      </c>
-      <c r="D94" t="s">
-        <v>150</v>
-      </c>
-      <c r="E94" t="s">
-        <v>11</v>
-      </c>
-      <c r="F94" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>21330051920027</v>
-      </c>
-      <c r="B95" t="s">
-        <v>94</v>
-      </c>
-      <c r="C95" t="s">
-        <v>118</v>
-      </c>
-      <c r="D95" t="s">
-        <v>134</v>
-      </c>
-      <c r="E95" t="s">
-        <v>7</v>
-      </c>
-      <c r="F95" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>21330051920027</v>
-      </c>
-      <c r="B96" t="s">
-        <v>94</v>
-      </c>
-      <c r="C96" t="s">
-        <v>118</v>
-      </c>
-      <c r="D96" t="s">
-        <v>134</v>
-      </c>
-      <c r="E96" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>21330051920027</v>
-      </c>
-      <c r="B97" t="s">
-        <v>94</v>
-      </c>
-      <c r="C97" t="s">
-        <v>118</v>
-      </c>
-      <c r="D97" t="s">
-        <v>134</v>
-      </c>
-      <c r="E97" t="s">
-        <v>11</v>
-      </c>
-      <c r="F97" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>21330051920028</v>
-      </c>
-      <c r="B98" t="s">
-        <v>95</v>
-      </c>
-      <c r="C98" t="s">
-        <v>119</v>
-      </c>
-      <c r="D98" t="s">
-        <v>151</v>
-      </c>
-      <c r="E98" t="s">
-        <v>7</v>
-      </c>
-      <c r="F98" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>21330051920028</v>
-      </c>
-      <c r="B99" t="s">
-        <v>95</v>
-      </c>
-      <c r="C99" t="s">
-        <v>119</v>
-      </c>
-      <c r="D99" t="s">
-        <v>151</v>
-      </c>
-      <c r="E99" t="s">
-        <v>5</v>
-      </c>
-      <c r="F99" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>21330051920028</v>
-      </c>
-      <c r="B100" t="s">
-        <v>95</v>
-      </c>
-      <c r="C100" t="s">
-        <v>119</v>
-      </c>
-      <c r="D100" t="s">
-        <v>151</v>
-      </c>
-      <c r="E100" t="s">
-        <v>11</v>
-      </c>
-      <c r="F100" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>21330051920393</v>
-      </c>
-      <c r="B101" t="s">
-        <v>96</v>
-      </c>
-      <c r="C101" t="s">
-        <v>120</v>
-      </c>
-      <c r="D101" t="s">
-        <v>152</v>
-      </c>
-      <c r="E101" t="s">
-        <v>7</v>
-      </c>
-      <c r="F101" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>21330051920393</v>
-      </c>
-      <c r="B102" t="s">
-        <v>96</v>
-      </c>
-      <c r="C102" t="s">
-        <v>120</v>
-      </c>
-      <c r="D102" t="s">
-        <v>152</v>
-      </c>
-      <c r="E102" t="s">
-        <v>5</v>
-      </c>
-      <c r="F102" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>21330051920393</v>
-      </c>
-      <c r="B103" t="s">
-        <v>96</v>
-      </c>
-      <c r="C103" t="s">
-        <v>120</v>
-      </c>
-      <c r="D103" t="s">
-        <v>152</v>
-      </c>
-      <c r="E103" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" t="s">
         <v>59</v>
       </c>
     </row>
@@ -8556,7 +7899,7 @@
         <v>128</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8573,7 +7916,7 @@
         <v>135</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8590,7 +7933,7 @@
         <v>142</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8607,7 +7950,7 @@
         <v>121</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8624,7 +7967,7 @@
         <v>122</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8641,7 +7984,7 @@
         <v>123</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8658,7 +8001,7 @@
         <v>124</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8675,7 +8018,7 @@
         <v>125</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8692,7 +8035,7 @@
         <v>126</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8709,7 +8052,7 @@
         <v>127</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8726,7 +8069,7 @@
         <v>129</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8743,7 +8086,7 @@
         <v>130</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -8760,7 +8103,7 @@
         <v>131</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8777,7 +8120,7 @@
         <v>132</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8794,7 +8137,7 @@
         <v>133</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8811,7 +8154,7 @@
         <v>134</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8828,7 +8171,7 @@
         <v>136</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8845,7 +8188,7 @@
         <v>137</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8862,7 +8205,7 @@
         <v>138</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8879,7 +8222,7 @@
         <v>139</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8896,7 +8239,7 @@
         <v>140</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8913,7 +8256,7 @@
         <v>141</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8930,7 +8273,7 @@
         <v>143</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8947,7 +8290,7 @@
         <v>144</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8964,7 +8307,7 @@
         <v>145</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8981,7 +8324,7 @@
         <v>146</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8998,7 +8341,7 @@
         <v>147</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -9015,7 +8358,7 @@
         <v>148</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -9032,7 +8375,7 @@
         <v>149</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -9049,7 +8392,7 @@
         <v>150</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -9066,7 +8409,7 @@
         <v>134</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -9083,7 +8426,7 @@
         <v>151</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -9100,7 +8443,7 @@
         <v>152</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9110,7 +8453,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9140,6 +8483,696 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920008</v>
+      </c>
+      <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920008</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920010</v>
+      </c>
+      <c r="B4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920010</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920011</v>
+      </c>
+      <c r="B6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920011</v>
+      </c>
+      <c r="B7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920013</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920013</v>
+      </c>
+      <c r="B9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920391</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920391</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920015</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920015</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920016</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920016</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920022</v>
+      </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" t="s">
+        <v>141</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920022</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920367</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920367</v>
+      </c>
+      <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920018</v>
+      </c>
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" t="s">
+        <v>145</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920018</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920019</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920019</v>
+      </c>
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920021</v>
+      </c>
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920021</v>
+      </c>
+      <c r="B25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" t="s">
+        <v>147</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920022</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" t="s">
+        <v>148</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920022</v>
+      </c>
+      <c r="B27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920025</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>21330051920025</v>
+      </c>
+      <c r="B29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>21330051920027</v>
+      </c>
+      <c r="B30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>21330051920027</v>
+      </c>
+      <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/4AEV - Estadisticos 20222.xlsx
+++ b/grupos/4AEV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="153">
   <si>
     <t>Materia</t>
   </si>
@@ -195,16 +195,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Desc Desc Desc</t>
   </si>
   <si>
     <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>NC</t>
@@ -985,7 +985,7 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -997,7 +997,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1048,7 +1048,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>5</v>
@@ -1060,7 +1060,7 @@
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1074,7 +1074,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -1086,7 +1086,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1137,7 +1137,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>5</v>
@@ -1149,7 +1149,7 @@
         <v>5</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1163,7 +1163,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -1175,7 +1175,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1226,7 +1226,7 @@
         <v>5</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z6">
         <v>6</v>
@@ -1238,7 +1238,7 @@
         <v>5</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1252,7 +1252,7 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1264,7 +1264,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1315,7 +1315,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -1327,7 +1327,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1341,7 +1341,7 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>8</v>
@@ -1353,7 +1353,7 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1404,7 +1404,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z8">
         <v>8</v>
@@ -1416,7 +1416,7 @@
         <v>8</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1430,7 +1430,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>5</v>
@@ -1442,7 +1442,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1493,7 +1493,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>5</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1519,7 +1519,7 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -1531,7 +1531,7 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1582,7 +1582,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z10">
         <v>8</v>
@@ -1594,7 +1594,7 @@
         <v>7</v>
       </c>
       <c r="AC10">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1608,7 +1608,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -1620,7 +1620,7 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1671,7 +1671,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>7</v>
@@ -1683,7 +1683,7 @@
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1697,10 +1697,10 @@
         <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -1709,7 +1709,7 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1760,10 +1760,10 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA12">
         <v>5</v>
@@ -1772,7 +1772,7 @@
         <v>5</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1786,7 +1786,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <v>8</v>
@@ -1798,7 +1798,7 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1849,7 +1849,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>8</v>
@@ -1861,7 +1861,7 @@
         <v>7</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1875,7 +1875,7 @@
         <v>6</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -1887,7 +1887,7 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1938,7 +1938,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -1950,7 +1950,7 @@
         <v>7</v>
       </c>
       <c r="AC14">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -1976,7 +1976,7 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -2027,7 +2027,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <v>5</v>
@@ -2039,7 +2039,7 @@
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2053,7 +2053,7 @@
         <v>6</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -2065,7 +2065,7 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2116,7 +2116,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>6</v>
@@ -2128,7 +2128,7 @@
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2142,7 +2142,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>6</v>
@@ -2154,7 +2154,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2205,7 +2205,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <v>6</v>
@@ -2217,7 +2217,7 @@
         <v>8</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2231,10 +2231,10 @@
         <v>5</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>4</v>
@@ -2243,7 +2243,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2294,10 +2294,10 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA18">
         <v>5</v>
@@ -2306,7 +2306,7 @@
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2320,7 +2320,7 @@
         <v>9</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E19">
         <v>9</v>
@@ -2332,7 +2332,7 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2383,7 +2383,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2395,7 +2395,7 @@
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2409,7 +2409,7 @@
         <v>6</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>8</v>
@@ -2421,7 +2421,7 @@
         <v>7</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2472,7 +2472,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z20">
         <v>8</v>
@@ -2484,7 +2484,7 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2498,7 +2498,7 @@
         <v>5</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2510,7 +2510,7 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2561,7 +2561,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2587,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>8</v>
@@ -2599,7 +2599,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2650,7 +2650,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <v>8</v>
@@ -2662,7 +2662,7 @@
         <v>9</v>
       </c>
       <c r="AC22">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2676,7 +2676,7 @@
         <v>8</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>6</v>
@@ -2688,7 +2688,7 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2739,7 +2739,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z23">
         <v>6</v>
@@ -2751,7 +2751,7 @@
         <v>9</v>
       </c>
       <c r="AC23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2759,7 +2759,7 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F24">
         <v>4</v>
@@ -2768,7 +2768,7 @@
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2795,7 +2795,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -2804,7 +2804,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2818,10 +2818,10 @@
         <v>6</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F25">
         <v>7</v>
@@ -2830,7 +2830,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2881,10 +2881,10 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -2893,7 +2893,7 @@
         <v>8</v>
       </c>
       <c r="AC25">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2907,7 +2907,7 @@
         <v>5</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F26">
         <v>7</v>
@@ -2916,7 +2916,7 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2961,7 +2961,7 @@
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA26">
         <v>7</v>
@@ -2970,7 +2970,7 @@
         <v>5</v>
       </c>
       <c r="AC26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2984,7 +2984,7 @@
         <v>6</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F27">
         <v>6</v>
@@ -2993,7 +2993,7 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -3038,7 +3038,7 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>6</v>
@@ -3047,7 +3047,7 @@
         <v>7</v>
       </c>
       <c r="AC27">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3061,7 +3061,7 @@
         <v>6</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>9</v>
@@ -3073,7 +3073,7 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -3124,7 +3124,7 @@
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>9</v>
@@ -3136,7 +3136,7 @@
         <v>7</v>
       </c>
       <c r="AC28">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3150,7 +3150,7 @@
         <v>8</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>9</v>
@@ -3162,7 +3162,7 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -3213,7 +3213,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z29">
         <v>9</v>
@@ -3225,7 +3225,7 @@
         <v>8</v>
       </c>
       <c r="AC29">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3239,7 +3239,7 @@
         <v>9</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -3251,7 +3251,7 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3302,7 +3302,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z30">
         <v>8</v>
@@ -3314,7 +3314,7 @@
         <v>9</v>
       </c>
       <c r="AC30">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3328,7 +3328,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E31">
         <v>8</v>
@@ -3340,7 +3340,7 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3391,7 +3391,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z31">
         <v>8</v>
@@ -3403,7 +3403,7 @@
         <v>8</v>
       </c>
       <c r="AC31">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3417,7 +3417,7 @@
         <v>6</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E32">
         <v>5</v>
@@ -3429,7 +3429,7 @@
         <v>5</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3480,7 +3480,7 @@
         <v>6</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z32">
         <v>5</v>
@@ -3492,7 +3492,7 @@
         <v>5</v>
       </c>
       <c r="AC32">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3506,7 +3506,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E33">
         <v>7</v>
@@ -3518,7 +3518,7 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3569,7 +3569,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z33">
         <v>7</v>
@@ -3581,7 +3581,7 @@
         <v>9</v>
       </c>
       <c r="AC33">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3595,7 +3595,7 @@
         <v>6</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -3607,7 +3607,7 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3658,7 +3658,7 @@
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z34">
         <v>6</v>
@@ -3670,7 +3670,7 @@
         <v>7</v>
       </c>
       <c r="AC34">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3684,7 +3684,7 @@
         <v>10</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E35">
         <v>9</v>
@@ -3696,7 +3696,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3747,7 +3747,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z35">
         <v>9</v>
@@ -3759,7 +3759,7 @@
         <v>7</v>
       </c>
       <c r="AC35">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3773,7 +3773,7 @@
         <v>6</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E36">
         <v>5</v>
@@ -3785,7 +3785,7 @@
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3836,7 +3836,7 @@
         <v>6</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z36">
         <v>5</v>
@@ -3848,7 +3848,7 @@
         <v>5</v>
       </c>
       <c r="AC36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3984,7 +3984,7 @@
         <v>95</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -3996,7 +3996,7 @@
         <v>76.7</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>95</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>66.7</v>
@@ -4064,7 +4064,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v>95</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>66.7</v>
@@ -4132,7 +4132,7 @@
         <v>80</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4188,7 +4188,7 @@
         <v>85</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>60</v>
@@ -4200,7 +4200,7 @@
         <v>76.7</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4256,7 +4256,7 @@
         <v>100</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>120</v>
@@ -4268,7 +4268,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4324,7 +4324,7 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>93.3</v>
@@ -4336,7 +4336,7 @@
         <v>83.3</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4392,7 +4392,7 @@
         <v>95</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -4404,7 +4404,7 @@
         <v>93.3</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4460,7 +4460,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>120</v>
@@ -4472,7 +4472,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -4528,7 +4528,7 @@
         <v>80</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4540,7 +4540,7 @@
         <v>66.7</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -4596,7 +4596,7 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>120</v>
@@ -4608,7 +4608,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -4664,7 +4664,7 @@
         <v>95</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>120</v>
@@ -4676,7 +4676,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -4732,7 +4732,7 @@
         <v>90</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>93.3</v>
@@ -4744,7 +4744,7 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -4800,7 +4800,7 @@
         <v>95</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -4812,7 +4812,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -4868,7 +4868,7 @@
         <v>95</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>120</v>
@@ -4880,7 +4880,7 @@
         <v>86.7</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -4936,7 +4936,7 @@
         <v>80</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4948,7 +4948,7 @@
         <v>86.7</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -5004,7 +5004,7 @@
         <v>100</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>120</v>
@@ -5016,7 +5016,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -5072,7 +5072,7 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>120</v>
@@ -5084,7 +5084,7 @@
         <v>93.3</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>26.7</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -5220,7 +5220,7 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -5276,7 +5276,7 @@
         <v>100</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -5288,7 +5288,7 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -5347,7 +5347,7 @@
         <v>66.7</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -5385,7 +5385,7 @@
         <v>95</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>93.3</v>
@@ -5397,7 +5397,7 @@
         <v>83.3</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5453,7 +5453,7 @@
         <v>90</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>66.7</v>
@@ -5462,7 +5462,7 @@
         <v>83.3</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -5512,7 +5512,7 @@
         <v>90</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>66.7</v>
@@ -5521,7 +5521,7 @@
         <v>86.7</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -5571,7 +5571,7 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>120</v>
@@ -5583,7 +5583,7 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -5639,7 +5639,7 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>120</v>
@@ -5651,7 +5651,7 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>100</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>120</v>
@@ -5719,7 +5719,7 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5775,7 +5775,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>120</v>
@@ -5787,7 +5787,7 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5843,7 +5843,7 @@
         <v>100</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>93.3</v>
@@ -5855,7 +5855,7 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -5911,7 +5911,7 @@
         <v>100</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>120</v>
@@ -5923,7 +5923,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>100</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>120</v>
@@ -5991,7 +5991,7 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -6047,7 +6047,7 @@
         <v>100</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E35">
         <v>106.7</v>
@@ -6059,7 +6059,7 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -6115,7 +6115,7 @@
         <v>100</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>120</v>
@@ -6127,7 +6127,7 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -6224,86 +6224,92 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>57.58</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>42.42</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>61.29</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>38.71</v>
+      </c>
+      <c r="H3">
+        <v>6.5</v>
       </c>
       <c r="I3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>57.58</v>
+        <v>71.88</v>
       </c>
       <c r="G4">
-        <v>42.42</v>
+        <v>28.13</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6314,60 +6320,60 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <v>9</v>
       </c>
       <c r="F5">
-        <v>58.06</v>
+        <v>72.73</v>
       </c>
       <c r="G5">
-        <v>29.03</v>
+        <v>27.27</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>12.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>9</v>
       </c>
       <c r="F6">
-        <v>71.88</v>
+        <v>72.73</v>
       </c>
       <c r="G6">
-        <v>28.13</v>
+        <v>27.27</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6378,28 +6384,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7">
         <v>24</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="G7">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6410,28 +6416,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8">
         <v>32</v>
       </c>
       <c r="D8">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6447,7 +6453,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6472,1386 +6478,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920001</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920003</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920003</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920005</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920005</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" t="s">
-        <v>124</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920005</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" t="s">
-        <v>124</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920008</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>99</v>
-      </c>
-      <c r="D10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920008</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" t="s">
-        <v>125</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920049</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920049</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920010</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920010</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920355</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920355</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" t="s">
-        <v>128</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920355</v>
-      </c>
-      <c r="B18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" t="s">
-        <v>128</v>
-      </c>
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920078</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920078</v>
-      </c>
-      <c r="B20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920011</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" t="s">
-        <v>130</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920011</v>
-      </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" t="s">
-        <v>130</v>
-      </c>
-      <c r="E22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920195</v>
-      </c>
-      <c r="B23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920195</v>
-      </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920012</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" t="s">
-        <v>132</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920012</v>
-      </c>
-      <c r="B26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" t="s">
-        <v>132</v>
-      </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920018</v>
-      </c>
-      <c r="B27" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920018</v>
-      </c>
-      <c r="B28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" t="s">
-        <v>133</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920013</v>
-      </c>
-      <c r="B29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" t="s">
-        <v>105</v>
-      </c>
-      <c r="D29" t="s">
-        <v>134</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920013</v>
-      </c>
-      <c r="B30" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" t="s">
-        <v>105</v>
-      </c>
-      <c r="D30" t="s">
-        <v>134</v>
-      </c>
-      <c r="E30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920019</v>
-      </c>
-      <c r="B31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D31" t="s">
-        <v>135</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920019</v>
-      </c>
-      <c r="B32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" t="s">
-        <v>135</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920019</v>
-      </c>
-      <c r="B33" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" t="s">
-        <v>106</v>
-      </c>
-      <c r="D33" t="s">
-        <v>135</v>
-      </c>
-      <c r="E33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920391</v>
-      </c>
-      <c r="B34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" t="s">
-        <v>107</v>
-      </c>
-      <c r="D34" t="s">
-        <v>136</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920391</v>
-      </c>
-      <c r="B35" t="s">
-        <v>80</v>
-      </c>
-      <c r="C35" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" t="s">
-        <v>136</v>
-      </c>
-      <c r="E35" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920015</v>
-      </c>
-      <c r="B36" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" t="s">
-        <v>137</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920015</v>
-      </c>
-      <c r="B37" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" t="s">
-        <v>137</v>
-      </c>
-      <c r="E37" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920088</v>
-      </c>
-      <c r="B38" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D38" t="s">
-        <v>138</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920088</v>
-      </c>
-      <c r="B39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" t="s">
-        <v>108</v>
-      </c>
-      <c r="D39" t="s">
-        <v>138</v>
-      </c>
-      <c r="E39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920016</v>
-      </c>
-      <c r="B40" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" t="s">
-        <v>139</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920016</v>
-      </c>
-      <c r="B41" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" t="s">
-        <v>109</v>
-      </c>
-      <c r="D41" t="s">
-        <v>139</v>
-      </c>
-      <c r="E41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920089</v>
-      </c>
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" t="s">
-        <v>110</v>
-      </c>
-      <c r="D42" t="s">
-        <v>140</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920089</v>
-      </c>
-      <c r="B43" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" t="s">
-        <v>110</v>
-      </c>
-      <c r="D43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920022</v>
-      </c>
-      <c r="B44" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" t="s">
-        <v>111</v>
-      </c>
-      <c r="D44" t="s">
-        <v>141</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920022</v>
-      </c>
-      <c r="B45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C45" t="s">
-        <v>111</v>
-      </c>
-      <c r="D45" t="s">
-        <v>141</v>
-      </c>
-      <c r="E45" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920379</v>
-      </c>
-      <c r="B46" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46" t="s">
-        <v>112</v>
-      </c>
-      <c r="D46" t="s">
-        <v>142</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920379</v>
-      </c>
-      <c r="B47" t="s">
-        <v>86</v>
-      </c>
-      <c r="C47" t="s">
-        <v>112</v>
-      </c>
-      <c r="D47" t="s">
-        <v>142</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920379</v>
-      </c>
-      <c r="B48" t="s">
-        <v>86</v>
-      </c>
-      <c r="C48" t="s">
-        <v>112</v>
-      </c>
-      <c r="D48" t="s">
-        <v>142</v>
-      </c>
-      <c r="E48" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920366</v>
-      </c>
-      <c r="B49" t="s">
-        <v>87</v>
-      </c>
-      <c r="C49" t="s">
-        <v>74</v>
-      </c>
-      <c r="D49" t="s">
-        <v>143</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920366</v>
-      </c>
-      <c r="B50" t="s">
-        <v>87</v>
-      </c>
-      <c r="C50" t="s">
-        <v>74</v>
-      </c>
-      <c r="D50" t="s">
-        <v>143</v>
-      </c>
-      <c r="E50" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920367</v>
-      </c>
-      <c r="B51" t="s">
-        <v>87</v>
-      </c>
-      <c r="C51" t="s">
-        <v>74</v>
-      </c>
-      <c r="D51" t="s">
-        <v>144</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920367</v>
-      </c>
-      <c r="B52" t="s">
-        <v>87</v>
-      </c>
-      <c r="C52" t="s">
-        <v>74</v>
-      </c>
-      <c r="D52" t="s">
-        <v>144</v>
-      </c>
-      <c r="E52" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920018</v>
-      </c>
-      <c r="B53" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" t="s">
-        <v>113</v>
-      </c>
-      <c r="D53" t="s">
-        <v>145</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920018</v>
-      </c>
-      <c r="B54" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" t="s">
-        <v>113</v>
-      </c>
-      <c r="D54" t="s">
-        <v>145</v>
-      </c>
-      <c r="E54" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920019</v>
-      </c>
-      <c r="B55" t="s">
-        <v>89</v>
-      </c>
-      <c r="C55" t="s">
-        <v>114</v>
-      </c>
-      <c r="D55" t="s">
-        <v>146</v>
-      </c>
-      <c r="E55" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920019</v>
-      </c>
-      <c r="B56" t="s">
-        <v>89</v>
-      </c>
-      <c r="C56" t="s">
-        <v>114</v>
-      </c>
-      <c r="D56" t="s">
-        <v>146</v>
-      </c>
-      <c r="E56" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920021</v>
-      </c>
-      <c r="B57" t="s">
-        <v>90</v>
-      </c>
-      <c r="C57" t="s">
-        <v>115</v>
-      </c>
-      <c r="D57" t="s">
-        <v>147</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920021</v>
-      </c>
-      <c r="B58" t="s">
-        <v>90</v>
-      </c>
-      <c r="C58" t="s">
-        <v>115</v>
-      </c>
-      <c r="D58" t="s">
-        <v>147</v>
-      </c>
-      <c r="E58" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920022</v>
-      </c>
-      <c r="B59" t="s">
-        <v>91</v>
-      </c>
-      <c r="C59" t="s">
-        <v>116</v>
-      </c>
-      <c r="D59" t="s">
-        <v>148</v>
-      </c>
-      <c r="E59" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920022</v>
-      </c>
-      <c r="B60" t="s">
-        <v>91</v>
-      </c>
-      <c r="C60" t="s">
-        <v>116</v>
-      </c>
-      <c r="D60" t="s">
-        <v>148</v>
-      </c>
-      <c r="E60" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920023</v>
-      </c>
-      <c r="B61" t="s">
-        <v>92</v>
-      </c>
-      <c r="C61" t="s">
-        <v>74</v>
-      </c>
-      <c r="D61" t="s">
-        <v>149</v>
-      </c>
-      <c r="E61" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920023</v>
-      </c>
-      <c r="B62" t="s">
-        <v>92</v>
-      </c>
-      <c r="C62" t="s">
-        <v>74</v>
-      </c>
-      <c r="D62" t="s">
-        <v>149</v>
-      </c>
-      <c r="E62" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920025</v>
-      </c>
-      <c r="B63" t="s">
-        <v>93</v>
-      </c>
-      <c r="C63" t="s">
-        <v>117</v>
-      </c>
-      <c r="D63" t="s">
-        <v>150</v>
-      </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920025</v>
-      </c>
-      <c r="B64" t="s">
-        <v>93</v>
-      </c>
-      <c r="C64" t="s">
-        <v>117</v>
-      </c>
-      <c r="D64" t="s">
-        <v>150</v>
-      </c>
-      <c r="E64" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920027</v>
-      </c>
-      <c r="B65" t="s">
-        <v>94</v>
-      </c>
-      <c r="C65" t="s">
-        <v>118</v>
-      </c>
-      <c r="D65" t="s">
-        <v>134</v>
-      </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920027</v>
-      </c>
-      <c r="B66" t="s">
-        <v>94</v>
-      </c>
-      <c r="C66" t="s">
-        <v>118</v>
-      </c>
-      <c r="D66" t="s">
-        <v>134</v>
-      </c>
-      <c r="E66" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920028</v>
-      </c>
-      <c r="B67" t="s">
-        <v>95</v>
-      </c>
-      <c r="C67" t="s">
-        <v>119</v>
-      </c>
-      <c r="D67" t="s">
-        <v>151</v>
-      </c>
-      <c r="E67" t="s">
-        <v>7</v>
-      </c>
-      <c r="F67" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920028</v>
-      </c>
-      <c r="B68" t="s">
-        <v>95</v>
-      </c>
-      <c r="C68" t="s">
-        <v>119</v>
-      </c>
-      <c r="D68" t="s">
-        <v>151</v>
-      </c>
-      <c r="E68" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920393</v>
-      </c>
-      <c r="B69" t="s">
-        <v>96</v>
-      </c>
-      <c r="C69" t="s">
-        <v>120</v>
-      </c>
-      <c r="D69" t="s">
-        <v>152</v>
-      </c>
-      <c r="E69" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920393</v>
-      </c>
-      <c r="B70" t="s">
-        <v>96</v>
-      </c>
-      <c r="C70" t="s">
-        <v>120</v>
-      </c>
-      <c r="D70" t="s">
-        <v>152</v>
-      </c>
-      <c r="E70" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -7887,376 +6513,376 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920355</v>
+        <v>21330051920001</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920019</v>
+        <v>21330051920003</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920379</v>
+        <v>21330051920005</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920001</v>
+        <v>20330051920005</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920003</v>
+        <v>21330051920008</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920005</v>
+        <v>20330051920049</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920005</v>
+        <v>21330051920010</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920008</v>
+        <v>21330051920355</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920049</v>
+        <v>20330051920078</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920010</v>
+        <v>21330051920011</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920078</v>
+        <v>21330051920195</v>
       </c>
       <c r="B12" t="s">
         <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920011</v>
+        <v>21330051920012</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920195</v>
+        <v>20330051920018</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920012</v>
+        <v>21330051920013</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920018</v>
+        <v>20330051920019</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920013</v>
+        <v>20330051920391</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920391</v>
+        <v>21330051920015</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920015</v>
+        <v>20330051920088</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920088</v>
+        <v>21330051920016</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920016</v>
+        <v>20330051920089</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920089</v>
+        <v>20330051920022</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920022</v>
+        <v>21330051920379</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8273,7 +6899,7 @@
         <v>143</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8290,7 +6916,7 @@
         <v>144</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8307,7 +6933,7 @@
         <v>145</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8324,7 +6950,7 @@
         <v>146</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8341,7 +6967,7 @@
         <v>147</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8358,7 +6984,7 @@
         <v>148</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8375,7 +7001,7 @@
         <v>149</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8392,7 +7018,7 @@
         <v>150</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8409,7 +7035,7 @@
         <v>134</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8426,7 +7052,7 @@
         <v>151</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8443,7 +7069,7 @@
         <v>152</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8453,7 +7079,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8485,692 +7111,278 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920008</v>
+        <v>21330051920005</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920008</v>
+        <v>21330051920005</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920010</v>
+        <v>20330051920089</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920010</v>
+        <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920011</v>
+        <v>21330051920023</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920011</v>
+        <v>21330051920023</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920013</v>
+        <v>20330051920078</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920013</v>
+        <v>21330051920012</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920391</v>
+        <v>20330051920018</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920391</v>
+        <v>20330051920022</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920015</v>
+        <v>21330051920379</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920015</v>
+        <v>21330051920028</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920016</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D14" t="s">
-        <v>139</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920016</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920022</v>
-      </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920022</v>
-      </c>
-      <c r="B17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" t="s">
-        <v>141</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920367</v>
-      </c>
-      <c r="B18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" t="s">
-        <v>144</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920367</v>
-      </c>
-      <c r="B19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" t="s">
-        <v>144</v>
-      </c>
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920018</v>
-      </c>
-      <c r="B20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" t="s">
-        <v>145</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920018</v>
-      </c>
-      <c r="B21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" t="s">
-        <v>145</v>
-      </c>
-      <c r="E21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920019</v>
-      </c>
-      <c r="B22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" t="s">
-        <v>146</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920019</v>
-      </c>
-      <c r="B23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" t="s">
-        <v>146</v>
-      </c>
-      <c r="E23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" t="s">
-        <v>59</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920021</v>
-      </c>
-      <c r="B24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" t="s">
-        <v>147</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920021</v>
-      </c>
-      <c r="B25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" t="s">
-        <v>147</v>
-      </c>
-      <c r="E25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" t="s">
-        <v>59</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920022</v>
-      </c>
-      <c r="B26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" t="s">
-        <v>148</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920022</v>
-      </c>
-      <c r="B27" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" t="s">
-        <v>116</v>
-      </c>
-      <c r="D27" t="s">
-        <v>148</v>
-      </c>
-      <c r="E27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" t="s">
-        <v>59</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920025</v>
-      </c>
-      <c r="B28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" t="s">
-        <v>117</v>
-      </c>
-      <c r="D28" t="s">
-        <v>150</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>58</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920025</v>
-      </c>
-      <c r="B29" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" t="s">
-        <v>117</v>
-      </c>
-      <c r="D29" t="s">
-        <v>150</v>
-      </c>
-      <c r="E29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" t="s">
-        <v>59</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920027</v>
-      </c>
-      <c r="B30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" t="s">
-        <v>134</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>58</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920027</v>
-      </c>
-      <c r="B31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" t="s">
-        <v>134</v>
-      </c>
-      <c r="E31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" t="s">
-        <v>59</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4AEV - Estadisticos 20222.xlsx
+++ b/grupos/4AEV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="156">
   <si>
     <t>Materia</t>
   </si>
@@ -201,10 +201,19 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Barañon Samaniego Graciela de los Ángeles</t>
   </si>
   <si>
     <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
     <t>NC</t>
@@ -6355,7 +6364,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6">
         <v>33</v>
@@ -6387,7 +6396,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C7">
         <v>32</v>
@@ -6419,7 +6428,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C8">
         <v>32</v>
@@ -6462,16 +6471,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6496,16 +6505,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>56</v>
@@ -6516,13 +6525,13 @@
         <v>21330051920001</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -6533,13 +6542,13 @@
         <v>21330051920003</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6550,13 +6559,13 @@
         <v>21330051920005</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -6567,13 +6576,13 @@
         <v>20330051920005</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6584,13 +6593,13 @@
         <v>21330051920008</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6601,13 +6610,13 @@
         <v>20330051920049</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6618,13 +6627,13 @@
         <v>21330051920010</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6635,13 +6644,13 @@
         <v>21330051920355</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6652,13 +6661,13 @@
         <v>20330051920078</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6669,13 +6678,13 @@
         <v>21330051920011</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6686,13 +6695,13 @@
         <v>21330051920195</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6703,13 +6712,13 @@
         <v>21330051920012</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6720,13 +6729,13 @@
         <v>20330051920018</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6737,13 +6746,13 @@
         <v>21330051920013</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -6754,13 +6763,13 @@
         <v>20330051920019</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6771,13 +6780,13 @@
         <v>20330051920391</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6788,13 +6797,13 @@
         <v>21330051920015</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6805,13 +6814,13 @@
         <v>20330051920088</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6822,13 +6831,13 @@
         <v>21330051920016</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6839,13 +6848,13 @@
         <v>20330051920089</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6856,13 +6865,13 @@
         <v>20330051920022</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6873,13 +6882,13 @@
         <v>21330051920379</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6890,13 +6899,13 @@
         <v>20330051920366</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6907,13 +6916,13 @@
         <v>20330051920367</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6924,13 +6933,13 @@
         <v>21330051920018</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6941,13 +6950,13 @@
         <v>21330051920019</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6958,13 +6967,13 @@
         <v>21330051920021</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6975,13 +6984,13 @@
         <v>21330051920022</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6992,13 +7001,13 @@
         <v>21330051920023</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -7009,13 +7018,13 @@
         <v>21330051920025</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -7026,13 +7035,13 @@
         <v>21330051920027</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -7043,13 +7052,13 @@
         <v>21330051920028</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -7060,13 +7069,13 @@
         <v>21330051920393</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -7088,16 +7097,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7114,13 +7123,13 @@
         <v>21330051920005</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -7137,13 +7146,13 @@
         <v>21330051920005</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -7160,19 +7169,19 @@
         <v>20330051920089</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7183,13 +7192,13 @@
         <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -7206,13 +7215,13 @@
         <v>21330051920023</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -7229,13 +7238,13 @@
         <v>21330051920023</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -7252,13 +7261,13 @@
         <v>20330051920078</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -7275,13 +7284,13 @@
         <v>21330051920012</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -7298,13 +7307,13 @@
         <v>20330051920018</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -7321,13 +7330,13 @@
         <v>20330051920022</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -7344,13 +7353,13 @@
         <v>21330051920379</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -7367,19 +7376,19 @@
         <v>21330051920028</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>5</v>

--- a/grupos/4AEV - Estadisticos 20222.xlsx
+++ b/grupos/4AEV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="90">
   <si>
     <t>Materia</t>
   </si>
@@ -201,15 +200,15 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Barañon Samaniego Graciela de los Ángeles</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
@@ -228,271 +227,76 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAVIER</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
   </si>
   <si>
     <t>DULIAM</t>
   </si>
   <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
     <t>ARIEL</t>
   </si>
   <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
     <t>OMAR</t>
   </si>
   <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
-    <t>ELIAS</t>
-  </si>
-  <si>
-    <t>DAVID DANIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
     <t>MIGUEL</t>
   </si>
   <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>GERSON UZIEL</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
     <t>JAFET</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -545,11 +349,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1012,7 +817,7 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1027,7 +832,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1101,7 +906,7 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1116,7 +921,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1143,7 +948,7 @@
         <v>6</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1190,7 +995,7 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1205,7 +1010,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1247,7 +1052,7 @@
         <v>5</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1279,7 +1084,7 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1294,7 +1099,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1368,7 +1173,7 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1383,7 +1188,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1457,7 +1262,7 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1472,7 +1277,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1499,7 +1304,7 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1546,7 +1351,7 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1561,7 +1366,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1588,7 +1393,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1635,7 +1440,7 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1650,7 +1455,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1692,7 +1497,7 @@
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1724,7 +1529,7 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1739,7 +1544,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1813,7 +1618,7 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1828,7 +1633,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1855,7 +1660,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1870,7 +1675,7 @@
         <v>7</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1902,7 +1707,7 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1917,7 +1722,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1959,7 +1764,7 @@
         <v>7</v>
       </c>
       <c r="AC14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1991,7 +1796,7 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -2006,7 +1811,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -2048,7 +1853,7 @@
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2080,7 +1885,7 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -2095,7 +1900,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2122,7 +1927,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2169,7 +1974,7 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2184,7 +1989,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2226,7 +2031,7 @@
         <v>8</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2258,7 +2063,7 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2273,7 +2078,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2347,7 +2152,7 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2362,7 +2167,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2389,7 +2194,7 @@
         <v>10</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2436,7 +2241,7 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2451,7 +2256,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2478,7 +2283,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2493,7 +2298,7 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2525,7 +2330,7 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2540,7 +2345,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2614,7 +2419,7 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2629,7 +2434,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2656,7 +2461,7 @@
         <v>9</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2703,7 +2508,7 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2718,7 +2523,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2745,7 +2550,7 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2760,7 +2565,7 @@
         <v>9</v>
       </c>
       <c r="AC23">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2789,7 +2594,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2813,7 +2618,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2845,7 +2650,7 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2860,7 +2665,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2902,7 +2707,7 @@
         <v>8</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2931,7 +2736,7 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2943,7 +2748,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2967,7 +2772,7 @@
         <v>6</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -3008,7 +2813,7 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -3020,7 +2825,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3044,7 +2849,7 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -3056,7 +2861,7 @@
         <v>7</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3088,7 +2893,7 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -3103,7 +2908,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3130,7 +2935,7 @@
         <v>6</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -3145,7 +2950,7 @@
         <v>7</v>
       </c>
       <c r="AC28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3177,7 +2982,7 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -3192,7 +2997,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3219,7 +3024,7 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -3234,7 +3039,7 @@
         <v>8</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3266,7 +3071,7 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3281,7 +3086,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3355,7 +3160,7 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3370,7 +3175,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3412,7 +3217,7 @@
         <v>8</v>
       </c>
       <c r="AC31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3444,7 +3249,7 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3459,7 +3264,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3486,7 +3291,7 @@
         <v>6</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>6</v>
@@ -3501,7 +3306,7 @@
         <v>5</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3533,7 +3338,7 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3548,7 +3353,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3575,7 +3380,7 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3622,7 +3427,7 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3637,7 +3442,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3664,7 +3469,7 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>6</v>
@@ -3711,7 +3516,7 @@
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3726,7 +3531,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3800,7 +3605,7 @@
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3815,7 +3620,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3842,7 +3647,7 @@
         <v>5</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -4011,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -4026,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -4079,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -4094,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -4147,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -4162,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -4230,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -4283,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -4298,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -4351,7 +4156,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -4366,7 +4171,7 @@
         <v>0</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -4419,7 +4224,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -4434,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -4487,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -4502,7 +4307,7 @@
         <v>0</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -4555,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -4570,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -4623,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -4638,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -4691,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -4706,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -4759,7 +4564,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -4774,7 +4579,7 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -4827,7 +4632,7 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -4842,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -4895,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -4910,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4963,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -4978,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -5031,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -5046,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -5099,7 +4904,7 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -5114,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -5182,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -5235,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -5250,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -5303,7 +5108,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -5318,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5368,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -5412,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -5427,7 +5232,7 @@
         <v>0</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -5477,7 +5282,7 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -5489,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>63.3</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5536,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -5548,7 +5353,7 @@
         <v>0</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5598,7 +5403,7 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -5613,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -5666,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -5681,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -5734,7 +5539,7 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -5749,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -5802,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -5817,7 +5622,7 @@
         <v>0</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -5870,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -5885,7 +5690,7 @@
         <v>0</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -5938,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -5953,7 +5758,7 @@
         <v>0</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -6006,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -6021,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -6074,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -6089,7 +5894,7 @@
         <v>0</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -6142,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -6157,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -6197,6 +6002,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -6247,11 +6054,11 @@
       <c r="E2">
         <v>14</v>
       </c>
-      <c r="F2">
-        <v>57.58</v>
-      </c>
-      <c r="G2">
-        <v>42.42</v>
+      <c r="F2" s="2">
+        <v>57.6</v>
+      </c>
+      <c r="G2" s="2">
+        <v>42.4</v>
       </c>
       <c r="H2">
         <v>6.6</v>
@@ -6259,7 +6066,7 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6279,11 +6086,11 @@
       <c r="E3">
         <v>12</v>
       </c>
-      <c r="F3">
-        <v>61.29</v>
-      </c>
-      <c r="G3">
-        <v>38.71</v>
+      <c r="F3" s="2">
+        <v>61.3</v>
+      </c>
+      <c r="G3" s="2">
+        <v>38.7</v>
       </c>
       <c r="H3">
         <v>6.5</v>
@@ -6291,45 +6098,45 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <v>71.88</v>
-      </c>
-      <c r="G4">
-        <v>28.13</v>
+        <v>11</v>
+      </c>
+      <c r="F4" s="2">
+        <v>66.7</v>
+      </c>
+      <c r="G4" s="2">
+        <v>33.3</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -6343,51 +6150,51 @@
       <c r="E5">
         <v>9</v>
       </c>
-      <c r="F5">
-        <v>72.73</v>
-      </c>
-      <c r="G5">
-        <v>27.27</v>
+      <c r="F5" s="2">
+        <v>72.7</v>
+      </c>
+      <c r="G5" s="2">
+        <v>27.3</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>24</v>
       </c>
       <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>72.73</v>
-      </c>
-      <c r="G6">
-        <v>27.27</v>
+        <v>8</v>
+      </c>
+      <c r="F6" s="2">
+        <v>75</v>
+      </c>
+      <c r="G6" s="2">
+        <v>25</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6407,10 +6214,10 @@
       <c r="E7">
         <v>8</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>75</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>25</v>
       </c>
       <c r="H7">
@@ -6419,7 +6226,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6439,10 +6246,10 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8">
+      <c r="F8" s="2">
+        <v>100</v>
+      </c>
+      <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8">
@@ -6451,7 +6258,7 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6496,599 +6303,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21330051920001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>21330051920003</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>21330051920005</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>20330051920005</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>21330051920008</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>20330051920049</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>21330051920010</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>21330051920355</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>20330051920078</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>21330051920011</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>21330051920195</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>21330051920012</v>
-      </c>
-      <c r="B13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
-        <v>135</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>20330051920018</v>
-      </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>21330051920013</v>
-      </c>
-      <c r="B15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>20330051920019</v>
-      </c>
-      <c r="B16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>20330051920391</v>
-      </c>
-      <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" t="s">
-        <v>139</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>21330051920015</v>
-      </c>
-      <c r="B18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" t="s">
-        <v>140</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>20330051920088</v>
-      </c>
-      <c r="B19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>21330051920016</v>
-      </c>
-      <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" t="s">
-        <v>142</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>20330051920089</v>
-      </c>
-      <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>20330051920022</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>21330051920379</v>
-      </c>
-      <c r="B23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>20330051920366</v>
-      </c>
-      <c r="B24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" t="s">
-        <v>146</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>20330051920367</v>
-      </c>
-      <c r="B25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" t="s">
-        <v>147</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>21330051920018</v>
-      </c>
-      <c r="B26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" t="s">
-        <v>148</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>21330051920019</v>
-      </c>
-      <c r="B27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" t="s">
-        <v>149</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>21330051920021</v>
-      </c>
-      <c r="B28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" t="s">
-        <v>150</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>21330051920022</v>
-      </c>
-      <c r="B29" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" t="s">
-        <v>151</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>21330051920023</v>
-      </c>
-      <c r="B30" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" t="s">
-        <v>152</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>21330051920025</v>
-      </c>
-      <c r="B31" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" t="s">
-        <v>153</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>21330051920027</v>
-      </c>
-      <c r="B32" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" t="s">
-        <v>137</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>21330051920028</v>
-      </c>
-      <c r="B33" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" t="s">
-        <v>154</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>21330051920393</v>
-      </c>
-      <c r="B34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" t="s">
-        <v>155</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7120,22 +6335,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920005</v>
+        <v>20330051920089</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7143,16 +6358,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920005</v>
+        <v>20330051920089</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -7166,22 +6381,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920089</v>
+        <v>20330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7189,22 +6404,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920089</v>
+        <v>20330051920366</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7215,13 +6430,13 @@
         <v>21330051920023</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -7238,13 +6453,13 @@
         <v>21330051920023</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -7261,13 +6476,13 @@
         <v>20330051920078</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -7284,13 +6499,13 @@
         <v>21330051920012</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -7304,19 +6519,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920018</v>
+        <v>21330051920013</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>60</v>
@@ -7327,22 +6542,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920022</v>
+        <v>21330051920379</v>
       </c>
       <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
         <v>88</v>
       </c>
-      <c r="C11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D11" t="s">
-        <v>144</v>
-      </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7350,47 +6565,24 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920379</v>
+        <v>21330051920028</v>
       </c>
       <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
         <v>89</v>
       </c>
-      <c r="C12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" t="s">
-        <v>145</v>
-      </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920028</v>
-      </c>
-      <c r="B13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" t="s">
-        <v>154</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEV - Estadisticos 20222.xlsx
+++ b/grupos/4AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
   </si>
   <si>
     <t>JAFET</t>
@@ -826,7 +829,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -915,7 +918,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1004,7 +1007,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1046,7 +1049,7 @@
         <v>6</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB6">
         <v>5</v>
@@ -1093,7 +1096,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1182,7 +1185,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1271,7 +1274,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1360,7 +1363,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1402,7 +1405,7 @@
         <v>8</v>
       </c>
       <c r="AA10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB10">
         <v>7</v>
@@ -1449,7 +1452,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1538,7 +1541,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1627,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1716,7 +1719,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1805,7 +1808,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1847,7 +1850,7 @@
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB15">
         <v>5</v>
@@ -1894,7 +1897,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1936,7 +1939,7 @@
         <v>6</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB16">
         <v>5</v>
@@ -1983,7 +1986,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2025,7 +2028,7 @@
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>8</v>
@@ -2072,7 +2075,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2161,7 +2164,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2250,7 +2253,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2292,7 +2295,7 @@
         <v>8</v>
       </c>
       <c r="AA20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB20">
         <v>7</v>
@@ -2339,7 +2342,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2428,7 +2431,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2517,7 +2520,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2588,7 +2591,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2659,7 +2662,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2701,7 +2704,7 @@
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB25">
         <v>8</v>
@@ -2742,7 +2745,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2778,7 +2781,7 @@
         <v>6</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>5</v>
@@ -2819,7 +2822,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2855,7 +2858,7 @@
         <v>6</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB27">
         <v>7</v>
@@ -2902,7 +2905,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2944,7 +2947,7 @@
         <v>9</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB28">
         <v>7</v>
@@ -2991,7 +2994,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3080,7 +3083,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3169,7 +3172,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3211,7 +3214,7 @@
         <v>8</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB31">
         <v>8</v>
@@ -3258,7 +3261,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3347,7 +3350,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3436,7 +3439,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3525,7 +3528,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3614,7 +3617,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3825,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3893,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3961,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -4029,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -4097,7 +4100,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -4165,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -4233,7 +4236,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -4301,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -4369,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4437,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4505,7 +4508,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4573,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4641,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4709,7 +4712,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4777,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4845,7 +4848,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4913,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -5049,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -5117,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -5167,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -5226,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -5288,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -5347,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>53.3</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -5412,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -5480,7 +5483,7 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5548,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5616,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5684,7 +5687,7 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5752,7 +5755,7 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5820,7 +5823,7 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -5888,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -5956,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -6303,7 +6306,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6565,24 +6568,47 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920028</v>
+        <v>20330051920367</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
         <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920028</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
         <v>63</v>
       </c>
-      <c r="G12">
+      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEV - Estadisticos 20222.xlsx
+++ b/grupos/4AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>Materia</t>
   </si>
@@ -194,6 +194,9 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
@@ -212,9 +215,6 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -227,67 +227,70 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>MIXCOHA</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
   </si>
   <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
+    <t>DE JESUS</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>ALEJANDRO</t>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>OMAR</t>
   </si>
   <si>
     <t>ELI ANTONIO</t>
   </si>
   <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>OMAR</t>
+    <t>EDGAR</t>
   </si>
   <si>
     <t>MIGUEL</t>
   </si>
   <si>
     <t>ISAAC</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
   </si>
   <si>
     <t>JAFET</t>
@@ -823,10 +826,10 @@
         <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -865,7 +868,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z4">
         <v>5</v>
@@ -912,10 +915,10 @@
         <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -954,7 +957,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z5">
         <v>5</v>
@@ -1001,10 +1004,10 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -1090,10 +1093,10 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>4</v>
@@ -1132,7 +1135,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -1179,10 +1182,10 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>9</v>
@@ -1221,7 +1224,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>8</v>
@@ -1268,10 +1271,10 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1310,7 +1313,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z9">
         <v>5</v>
@@ -1357,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
         <v>6</v>
@@ -1399,7 +1402,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>8</v>
@@ -1446,10 +1449,10 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>9</v>
@@ -1488,10 +1491,10 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -1535,10 +1538,10 @@
         <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -1577,7 +1580,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1624,10 +1627,10 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>9</v>
@@ -1666,7 +1669,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>8</v>
@@ -1713,10 +1716,10 @@
         <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>9</v>
@@ -1755,7 +1758,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -1802,10 +1805,10 @@
         <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -1891,10 +1894,10 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -1933,10 +1936,10 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>9</v>
@@ -1980,10 +1983,10 @@
         <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>9</v>
@@ -2022,10 +2025,10 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -2069,10 +2072,10 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>4</v>
@@ -2111,7 +2114,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z18">
         <v>5</v>
@@ -2158,10 +2161,10 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -2247,10 +2250,10 @@
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -2336,10 +2339,10 @@
         <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -2378,7 +2381,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -2425,10 +2428,10 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -2467,7 +2470,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>8</v>
@@ -2514,10 +2517,10 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -2556,10 +2559,10 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA23">
         <v>10</v>
@@ -2588,7 +2591,7 @@
         <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>4</v>
@@ -2612,7 +2615,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -2656,10 +2659,10 @@
         <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>9</v>
@@ -2698,7 +2701,7 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>5</v>
@@ -2742,7 +2745,7 @@
         <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>9</v>
@@ -2819,7 +2822,7 @@
         <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -2899,10 +2902,10 @@
         <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>7</v>
@@ -2941,10 +2944,10 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA28">
         <v>9</v>
@@ -2988,10 +2991,10 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -3030,7 +3033,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z29">
         <v>9</v>
@@ -3077,10 +3080,10 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3119,7 +3122,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z30">
         <v>8</v>
@@ -3166,10 +3169,10 @@
         <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>8</v>
@@ -3255,10 +3258,10 @@
         <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>8</v>
@@ -3297,7 +3300,7 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z32">
         <v>5</v>
@@ -3344,10 +3347,10 @@
         <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3386,10 +3389,10 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA33">
         <v>10</v>
@@ -3433,10 +3436,10 @@
         <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>7</v>
@@ -3475,10 +3478,10 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>7</v>
@@ -3522,10 +3525,10 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -3564,7 +3567,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z35">
         <v>9</v>
@@ -3611,10 +3614,10 @@
         <v>5</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
         <v>4</v>
@@ -3653,7 +3656,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z36">
         <v>5</v>
@@ -3822,10 +3825,10 @@
         <v>85</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="M4">
         <v>50</v>
@@ -3890,10 +3893,10 @@
         <v>85</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M5">
         <v>60</v>
@@ -3958,10 +3961,10 @@
         <v>85</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="M6">
         <v>60</v>
@@ -4026,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -4094,10 +4097,10 @@
         <v>95</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M8">
         <v>80</v>
@@ -4162,10 +4165,10 @@
         <v>85</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="M9">
         <v>6.7</v>
@@ -4230,10 +4233,10 @@
         <v>85</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M10">
         <v>60</v>
@@ -4298,10 +4301,10 @@
         <v>85</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="M11">
         <v>80</v>
@@ -4366,10 +4369,10 @@
         <v>80</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M12">
         <v>40</v>
@@ -4434,10 +4437,10 @@
         <v>95</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="M13">
         <v>66.7</v>
@@ -4502,10 +4505,10 @@
         <v>85</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
         <v>70</v>
@@ -4570,10 +4573,10 @@
         <v>85</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M15">
         <v>66.7</v>
@@ -4638,10 +4641,10 @@
         <v>85</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M16">
         <v>66.7</v>
@@ -4706,10 +4709,10 @@
         <v>85</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="M17">
         <v>73.3</v>
@@ -4774,10 +4777,10 @@
         <v>80</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>20</v>
@@ -4842,10 +4845,10 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M19">
         <v>83.3</v>
@@ -4910,10 +4913,10 @@
         <v>95</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M20">
         <v>70</v>
@@ -4978,7 +4981,7 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5046,10 +5049,10 @@
         <v>95</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M22">
         <v>73.3</v>
@@ -5114,10 +5117,10 @@
         <v>95</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="M23">
         <v>73.3</v>
@@ -5167,7 +5170,7 @@
         <v>86.7</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="M24">
         <v>16.7</v>
@@ -5223,10 +5226,10 @@
         <v>85</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M25">
         <v>66.7</v>
@@ -5288,7 +5291,7 @@
         <v>85</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M26">
         <v>60</v>
@@ -5347,7 +5350,7 @@
         <v>85</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M27">
         <v>53.3</v>
@@ -5409,10 +5412,10 @@
         <v>95</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M28">
         <v>73.3</v>
@@ -5477,10 +5480,10 @@
         <v>95</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M29">
         <v>83.3</v>
@@ -5545,10 +5548,10 @@
         <v>85</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="M30">
         <v>80</v>
@@ -5613,10 +5616,10 @@
         <v>95</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="M31">
         <v>73.3</v>
@@ -5681,10 +5684,10 @@
         <v>85</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="M32">
         <v>70</v>
@@ -5749,10 +5752,10 @@
         <v>95</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M33">
         <v>80</v>
@@ -5817,10 +5820,10 @@
         <v>85</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M34">
         <v>76.7</v>
@@ -5885,10 +5888,10 @@
         <v>90</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M35">
         <v>80</v>
@@ -5953,10 +5956,10 @@
         <v>85</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36">
         <v>60</v>
@@ -6043,28 +6046,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>57.6</v>
+        <v>56.2</v>
       </c>
       <c r="G2" s="2">
-        <v>42.4</v>
+        <v>43.8</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6075,28 +6078,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>19</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>61.3</v>
+        <v>57.6</v>
       </c>
       <c r="G3" s="2">
-        <v>38.7</v>
+        <v>42.4</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6107,28 +6110,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2">
-        <v>66.7</v>
+        <v>58.1</v>
       </c>
       <c r="G4" s="2">
-        <v>33.3</v>
+        <v>41.9</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6139,7 +6142,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -6148,19 +6151,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2">
-        <v>72.7</v>
+        <v>66.7</v>
       </c>
       <c r="G5" s="2">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6171,28 +6174,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>24</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="G6" s="2">
-        <v>25</v>
+        <v>27.3</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6203,7 +6206,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
@@ -6224,7 +6227,7 @@
         <v>25</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6235,7 +6238,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>64</v>
@@ -6244,19 +6247,19 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H8">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6306,7 +6309,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6338,7 +6341,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920089</v>
+        <v>20330051920078</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
@@ -6347,13 +6350,13 @@
         <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6361,7 +6364,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920089</v>
+        <v>20330051920078</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
@@ -6370,13 +6373,13 @@
         <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6384,19 +6387,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920366</v>
+        <v>21330051920012</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>58</v>
@@ -6407,22 +6410,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920366</v>
+        <v>21330051920012</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6430,22 +6433,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920023</v>
+        <v>21330051920013</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6453,22 +6456,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920023</v>
+        <v>21330051920013</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6476,19 +6479,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920078</v>
+        <v>20330051920366</v>
       </c>
       <c r="B8" t="s">
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>59</v>
@@ -6499,22 +6502,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920012</v>
+        <v>20330051920366</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
         <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6522,10 +6525,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920013</v>
+        <v>20330051920018</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
         <v>79</v>
@@ -6534,10 +6537,10 @@
         <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6548,7 +6551,7 @@
         <v>21330051920379</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
         <v>80</v>
@@ -6560,7 +6563,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6571,10 +6574,10 @@
         <v>20330051920367</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
         <v>89</v>
@@ -6583,7 +6586,7 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6591,10 +6594,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920028</v>
+        <v>21330051920018</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
         <v>81</v>
@@ -6603,12 +6606,35 @@
         <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920028</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEV - Estadisticos 20222.xlsx
+++ b/grupos/4AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="89">
   <si>
     <t>Materia</t>
   </si>
@@ -197,12 +197,12 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
@@ -248,9 +248,6 @@
     <t>PERALTA</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -266,9 +263,6 @@
     <t>GALLARDO</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
     <t>DULIAM</t>
   </si>
   <si>
@@ -291,9 +285,6 @@
   </si>
   <si>
     <t>CARLOS</t>
-  </si>
-  <si>
-    <t>JAFET</t>
   </si>
 </sst>
 </file>
@@ -820,7 +811,7 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -835,7 +826,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>5</v>
@@ -909,7 +900,7 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>8</v>
@@ -924,7 +915,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -966,7 +957,7 @@
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -998,7 +989,7 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -1013,7 +1004,7 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>5</v>
@@ -1087,7 +1078,7 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1102,7 +1093,7 @@
         <v>4</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -1176,7 +1167,7 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -1191,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -1218,7 +1209,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1265,7 +1256,7 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
         <v>10</v>
@@ -1280,7 +1271,7 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1307,7 +1298,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1354,7 +1345,7 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>8</v>
@@ -1369,7 +1360,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>8</v>
@@ -1411,7 +1402,7 @@
         <v>8</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -1443,7 +1434,7 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>7</v>
@@ -1458,7 +1449,7 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>8</v>
@@ -1485,7 +1476,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1500,7 +1491,7 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -1532,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -1547,7 +1538,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -1621,7 +1612,7 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>10</v>
@@ -1636,7 +1627,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>8</v>
@@ -1678,7 +1669,7 @@
         <v>10</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -1710,7 +1701,7 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>6</v>
@@ -1725,7 +1716,7 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -1752,7 +1743,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1799,7 +1790,7 @@
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -1814,7 +1805,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>5</v>
@@ -1888,7 +1879,7 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>8</v>
@@ -1903,7 +1894,7 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -1930,7 +1921,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -1977,7 +1968,7 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>7</v>
@@ -1992,7 +1983,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -2066,7 +2057,7 @@
         <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>5</v>
@@ -2081,7 +2072,7 @@
         <v>4</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -2155,7 +2146,7 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>10</v>
@@ -2170,7 +2161,7 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>8</v>
@@ -2244,7 +2235,7 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -2259,7 +2250,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>8</v>
@@ -2333,7 +2324,7 @@
         <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>5</v>
@@ -2348,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>5</v>
@@ -2422,7 +2413,7 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>10</v>
@@ -2437,7 +2428,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>8</v>
@@ -2479,7 +2470,7 @@
         <v>10</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>8</v>
@@ -2511,7 +2502,7 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
         <v>10</v>
@@ -2526,7 +2517,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>9</v>
@@ -2553,7 +2544,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -2568,7 +2559,7 @@
         <v>10</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -2597,7 +2588,7 @@
         <v>4</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>5</v>
@@ -2653,7 +2644,7 @@
         <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>6</v>
@@ -2668,7 +2659,7 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>9</v>
@@ -2710,7 +2701,7 @@
         <v>8</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>8</v>
@@ -2739,7 +2730,7 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>8</v>
@@ -2751,7 +2742,7 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>6</v>
@@ -2816,7 +2807,7 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -2828,7 +2819,7 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>6</v>
@@ -2896,7 +2887,7 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>7</v>
@@ -2911,7 +2902,7 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>8</v>
@@ -2938,7 +2929,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>7</v>
@@ -2953,7 +2944,7 @@
         <v>9</v>
       </c>
       <c r="AB28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC28">
         <v>8</v>
@@ -2985,7 +2976,7 @@
         <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
         <v>10</v>
@@ -3000,7 +2991,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -3027,7 +3018,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -3074,7 +3065,7 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>8</v>
@@ -3089,7 +3080,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
         <v>7</v>
@@ -3163,7 +3154,7 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>7</v>
@@ -3178,7 +3169,7 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
         <v>8</v>
@@ -3252,7 +3243,7 @@
         <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
         <v>7</v>
@@ -3267,7 +3258,7 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
         <v>5</v>
@@ -3341,7 +3332,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>9</v>
@@ -3356,7 +3347,7 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>8</v>
@@ -3383,7 +3374,7 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3430,7 +3421,7 @@
         <v>7</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>7</v>
@@ -3445,7 +3436,7 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <v>6</v>
@@ -3472,7 +3463,7 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>7</v>
@@ -3519,7 +3510,7 @@
         <v>9</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>10</v>
@@ -3534,7 +3525,7 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
         <v>9</v>
@@ -3561,7 +3552,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3576,7 +3567,7 @@
         <v>10</v>
       </c>
       <c r="AB35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC35">
         <v>9</v>
@@ -3608,7 +3599,7 @@
         <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
         <v>5</v>
@@ -3623,7 +3614,7 @@
         <v>4</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -3819,7 +3810,7 @@
         <v>83.3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>85</v>
@@ -3834,7 +3825,7 @@
         <v>50</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O4">
         <v>76.7</v>
@@ -3887,7 +3878,7 @@
         <v>76.7</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
         <v>85</v>
@@ -3902,7 +3893,7 @@
         <v>60</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O5">
         <v>83.3</v>
@@ -3955,7 +3946,7 @@
         <v>86.7</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>85</v>
@@ -3970,7 +3961,7 @@
         <v>60</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O6">
         <v>76.7</v>
@@ -4023,7 +4014,7 @@
         <v>73.3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -4038,7 +4029,7 @@
         <v>26.7</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O7">
         <v>56.7</v>
@@ -4091,7 +4082,7 @@
         <v>103.3</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
         <v>95</v>
@@ -4106,7 +4097,7 @@
         <v>80</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O8">
         <v>80</v>
@@ -4159,7 +4150,7 @@
         <v>90</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>85</v>
@@ -4174,7 +4165,7 @@
         <v>6.7</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O9">
         <v>76.7</v>
@@ -4227,7 +4218,7 @@
         <v>93.3</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>85</v>
@@ -4242,7 +4233,7 @@
         <v>60</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O10">
         <v>83.3</v>
@@ -4295,7 +4286,7 @@
         <v>86.7</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>85</v>
@@ -4310,7 +4301,7 @@
         <v>80</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O11">
         <v>86.7</v>
@@ -4363,7 +4354,7 @@
         <v>73.3</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>80</v>
@@ -4378,7 +4369,7 @@
         <v>40</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O12">
         <v>86.7</v>
@@ -4431,7 +4422,7 @@
         <v>93.3</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>95</v>
@@ -4446,7 +4437,7 @@
         <v>66.7</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O13">
         <v>80</v>
@@ -4499,7 +4490,7 @@
         <v>86.7</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
         <v>85</v>
@@ -4514,7 +4505,7 @@
         <v>70</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O14">
         <v>83.3</v>
@@ -4567,7 +4558,7 @@
         <v>96.7</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
         <v>85</v>
@@ -4582,7 +4573,7 @@
         <v>66.7</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O15">
         <v>80</v>
@@ -4635,7 +4626,7 @@
         <v>96.7</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>85</v>
@@ -4650,7 +4641,7 @@
         <v>66.7</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O16">
         <v>76.7</v>
@@ -4703,7 +4694,7 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
         <v>85</v>
@@ -4718,7 +4709,7 @@
         <v>73.3</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O17">
         <v>76.7</v>
@@ -4771,7 +4762,7 @@
         <v>73.3</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>80</v>
@@ -4786,7 +4777,7 @@
         <v>20</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O18">
         <v>86.7</v>
@@ -4839,7 +4830,7 @@
         <v>103.3</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -4854,7 +4845,7 @@
         <v>83.3</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O19">
         <v>86.7</v>
@@ -4907,7 +4898,7 @@
         <v>103.3</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
         <v>95</v>
@@ -4922,7 +4913,7 @@
         <v>70</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O20">
         <v>83.3</v>
@@ -4975,7 +4966,7 @@
         <v>50</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4990,7 +4981,7 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="O21">
         <v>30</v>
@@ -5043,7 +5034,7 @@
         <v>103.3</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
         <v>95</v>
@@ -5058,7 +5049,7 @@
         <v>73.3</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O22">
         <v>90</v>
@@ -5111,7 +5102,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
         <v>95</v>
@@ -5126,7 +5117,7 @@
         <v>73.3</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O23">
         <v>86.7</v>
@@ -5176,7 +5167,7 @@
         <v>16.7</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O24">
         <v>76.7</v>
@@ -5220,7 +5211,7 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>85</v>
@@ -5235,7 +5226,7 @@
         <v>66.7</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O25">
         <v>86.7</v>
@@ -5285,7 +5276,7 @@
         <v>83.3</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
         <v>85</v>
@@ -5297,7 +5288,7 @@
         <v>60</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O26">
         <v>63.3</v>
@@ -5344,7 +5335,7 @@
         <v>96.7</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
         <v>85</v>
@@ -5356,7 +5347,7 @@
         <v>53.3</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O27">
         <v>70</v>
@@ -5406,7 +5397,7 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
         <v>95</v>
@@ -5421,7 +5412,7 @@
         <v>73.3</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O28">
         <v>83.3</v>
@@ -5474,7 +5465,7 @@
         <v>103.3</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29">
         <v>95</v>
@@ -5489,7 +5480,7 @@
         <v>83.3</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O29">
         <v>86.7</v>
@@ -5542,7 +5533,7 @@
         <v>103.3</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30">
         <v>85</v>
@@ -5557,7 +5548,7 @@
         <v>80</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O30">
         <v>86.7</v>
@@ -5610,7 +5601,7 @@
         <v>96.7</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
         <v>95</v>
@@ -5625,7 +5616,7 @@
         <v>73.3</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O31">
         <v>80</v>
@@ -5678,7 +5669,7 @@
         <v>96.7</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32">
         <v>85</v>
@@ -5693,7 +5684,7 @@
         <v>70</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O32">
         <v>80</v>
@@ -5746,7 +5737,7 @@
         <v>103.3</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33">
         <v>95</v>
@@ -5761,7 +5752,7 @@
         <v>80</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O33">
         <v>86.7</v>
@@ -5814,7 +5805,7 @@
         <v>96.7</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34">
         <v>85</v>
@@ -5829,7 +5820,7 @@
         <v>76.7</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O34">
         <v>83.3</v>
@@ -5882,7 +5873,7 @@
         <v>103.3</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35">
         <v>90</v>
@@ -5897,7 +5888,7 @@
         <v>80</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O35">
         <v>90</v>
@@ -5950,7 +5941,7 @@
         <v>96.7</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J36">
         <v>85</v>
@@ -5965,7 +5956,7 @@
         <v>60</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O36">
         <v>73.3</v>
@@ -6078,25 +6069,25 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>57.6</v>
+        <v>58.1</v>
       </c>
       <c r="G3" s="2">
-        <v>42.4</v>
+        <v>41.9</v>
       </c>
       <c r="H3">
         <v>6.6</v>
@@ -6110,28 +6101,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <v>13</v>
       </c>
       <c r="F4" s="2">
-        <v>58.1</v>
+        <v>60.6</v>
       </c>
       <c r="G4" s="2">
-        <v>41.9</v>
+        <v>39.4</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6247,19 +6238,19 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>25</v>
+        <v>21.9</v>
       </c>
       <c r="H8">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6309,7 +6300,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6347,10 +6338,10 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -6370,16 +6361,16 @@
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6393,10 +6384,10 @@
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -6416,16 +6407,16 @@
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6439,10 +6430,10 @@
         <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -6462,10 +6453,10 @@
         <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -6488,13 +6479,13 @@
         <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6511,7 +6502,7 @@
         <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -6531,10 +6522,10 @@
         <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -6554,16 +6545,16 @@
         <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6580,7 +6571,7 @@
         <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -6600,10 +6591,10 @@
         <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -6612,29 +6603,6 @@
         <v>58</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920028</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEV - Estadisticos 20222.xlsx
+++ b/grupos/4AEV - Estadisticos 20222.xlsx
@@ -3789,7 +3789,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="C4">
         <v>95</v>
@@ -3801,55 +3801,55 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="G4">
         <v>76.7</v>
       </c>
       <c r="H4">
-        <v>83.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K4">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L4">
-        <v>113.3</v>
+        <v>47.2</v>
       </c>
       <c r="M4">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="N4">
-        <v>120</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O4">
-        <v>76.7</v>
+        <v>82.8</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>47.2</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3857,7 +3857,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -3866,58 +3866,58 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="F5">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5">
-        <v>76.7</v>
+        <v>74.2</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="J5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K5">
         <v>100</v>
       </c>
       <c r="L5">
-        <v>106.7</v>
+        <v>72.2</v>
       </c>
       <c r="M5">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="N5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>83.3</v>
+        <v>82.8</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3925,7 +3925,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C6">
         <v>95</v>
@@ -3934,58 +3934,58 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="F6">
-        <v>73.3</v>
+        <v>88</v>
       </c>
       <c r="G6">
         <v>80</v>
       </c>
       <c r="H6">
-        <v>86.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="J6">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>113.3</v>
+        <v>75</v>
       </c>
       <c r="M6">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="N6">
-        <v>120</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O6">
-        <v>76.7</v>
+        <v>84.5</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3993,7 +3993,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="C7">
         <v>85</v>
@@ -4002,58 +4002,58 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G7">
         <v>76.7</v>
       </c>
       <c r="H7">
-        <v>73.3</v>
+        <v>71</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M7">
-        <v>26.7</v>
+        <v>28</v>
       </c>
       <c r="N7">
-        <v>120</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O7">
-        <v>56.7</v>
+        <v>67.2</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4061,7 +4061,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -4070,58 +4070,58 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F8">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>100</v>
       </c>
       <c r="H8">
-        <v>103.3</v>
+        <v>100</v>
       </c>
       <c r="I8">
         <v>100</v>
       </c>
       <c r="J8">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>106.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M8">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="N8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>80</v>
+        <v>94.8</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4129,7 +4129,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -4138,58 +4138,58 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="F9">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G9">
         <v>83.3</v>
       </c>
       <c r="H9">
-        <v>90</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="J9">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="M9">
-        <v>6.7</v>
+        <v>52</v>
       </c>
       <c r="N9">
-        <v>120</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O9">
-        <v>76.7</v>
+        <v>86.2</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4197,7 +4197,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C10">
         <v>95</v>
@@ -4206,58 +4206,58 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="F10">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="G10">
         <v>93.3</v>
       </c>
       <c r="H10">
-        <v>93.3</v>
+        <v>90.3</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="J10">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>106.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="M10">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="N10">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="O10">
-        <v>83.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4265,7 +4265,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4274,58 +4274,58 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>100</v>
       </c>
       <c r="H11">
-        <v>86.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="J11">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>113.3</v>
+        <v>97.2</v>
       </c>
       <c r="M11">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="N11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>86.7</v>
+        <v>89.7</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4333,7 +4333,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>85</v>
+        <v>70.8</v>
       </c>
       <c r="C12">
         <v>80</v>
@@ -4345,16 +4345,16 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="G12">
         <v>66.7</v>
       </c>
       <c r="H12">
-        <v>73.3</v>
+        <v>71</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="J12">
         <v>80</v>
@@ -4363,37 +4363,37 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>106.7</v>
+        <v>44.4</v>
       </c>
       <c r="M12">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="N12">
-        <v>120</v>
+        <v>84.8</v>
       </c>
       <c r="O12">
-        <v>86.7</v>
+        <v>82.8</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>84.8</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4401,7 +4401,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -4410,58 +4410,58 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>100</v>
       </c>
       <c r="H13">
-        <v>93.3</v>
+        <v>90.3</v>
       </c>
       <c r="I13">
         <v>100</v>
       </c>
       <c r="J13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>113.3</v>
+        <v>97.2</v>
       </c>
       <c r="M13">
-        <v>66.7</v>
+        <v>90</v>
       </c>
       <c r="N13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>80</v>
+        <v>89.7</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4469,7 +4469,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>95</v>
@@ -4478,58 +4478,58 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G14">
         <v>100</v>
       </c>
       <c r="H14">
-        <v>86.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I14">
         <v>100</v>
       </c>
       <c r="J14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="M14">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="N14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>83.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4537,7 +4537,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="C15">
         <v>90</v>
@@ -4546,58 +4546,58 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="F15">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="G15">
         <v>100</v>
       </c>
       <c r="H15">
-        <v>96.7</v>
+        <v>93.5</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J15">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
+        <v>72.2</v>
+      </c>
+      <c r="M15">
         <v>80</v>
       </c>
-      <c r="M15">
-        <v>66.7</v>
-      </c>
       <c r="N15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O15">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="P15">
+        <v>95.5</v>
+      </c>
+      <c r="Q15">
+        <v>87.5</v>
+      </c>
+      <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
+        <v>72.2</v>
+      </c>
+      <c r="T15">
         <v>80</v>
       </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4605,7 +4605,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="C16">
         <v>95</v>
@@ -4614,58 +4614,58 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="F16">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G16">
         <v>100</v>
       </c>
       <c r="H16">
-        <v>96.7</v>
+        <v>93.5</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J16">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16">
-        <v>106.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="M16">
-        <v>66.7</v>
+        <v>88</v>
       </c>
       <c r="N16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>76.7</v>
+        <v>89.7</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4673,7 +4673,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C17">
         <v>95</v>
@@ -4682,58 +4682,58 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F17">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G17">
         <v>86.7</v>
       </c>
       <c r="H17">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="J17">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K17">
         <v>100</v>
       </c>
       <c r="L17">
-        <v>113.3</v>
+        <v>97.2</v>
       </c>
       <c r="M17">
-        <v>73.3</v>
+        <v>86</v>
       </c>
       <c r="N17">
-        <v>120</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O17">
-        <v>76.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4741,7 +4741,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C18">
         <v>80</v>
@@ -4753,16 +4753,16 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="G18">
         <v>86.7</v>
       </c>
       <c r="H18">
-        <v>73.3</v>
+        <v>71</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J18">
         <v>80</v>
@@ -4771,37 +4771,37 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="M18">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="N18">
-        <v>120</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O18">
-        <v>86.7</v>
+        <v>82.8</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4809,7 +4809,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -4818,16 +4818,16 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F19">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>100</v>
       </c>
       <c r="H19">
-        <v>103.3</v>
+        <v>100</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -4839,37 +4839,37 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>86.7</v>
+        <v>98.3</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4877,7 +4877,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -4886,58 +4886,58 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F20">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>93.3</v>
       </c>
       <c r="H20">
-        <v>103.3</v>
+        <v>100</v>
       </c>
       <c r="I20">
         <v>100</v>
       </c>
       <c r="J20">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>106.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M20">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="N20">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="O20">
-        <v>83.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4945,7 +4945,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -4957,55 +4957,55 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="G21">
         <v>26.7</v>
       </c>
       <c r="H21">
-        <v>50</v>
+        <v>48.4</v>
       </c>
       <c r="I21">
-        <v>50</v>
+        <v>59.1</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N21">
-        <v>66.7</v>
+        <v>42.4</v>
       </c>
       <c r="O21">
-        <v>30</v>
+        <v>41.4</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>59.1</v>
       </c>
       <c r="Q21">
         <v>0</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S21">
         <v>0</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>42.4</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5013,7 +5013,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -5022,58 +5022,58 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="F22">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G22">
         <v>100</v>
       </c>
       <c r="H22">
-        <v>103.3</v>
+        <v>100</v>
       </c>
       <c r="I22">
         <v>100</v>
       </c>
       <c r="J22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K22">
         <v>100</v>
       </c>
       <c r="L22">
-        <v>106.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="M22">
-        <v>73.3</v>
+        <v>92</v>
       </c>
       <c r="N22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5081,7 +5081,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -5090,58 +5090,58 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="F23">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>100</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I23">
         <v>100</v>
       </c>
       <c r="J23">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K23">
         <v>100</v>
       </c>
       <c r="L23">
-        <v>113.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M23">
-        <v>73.3</v>
+        <v>94</v>
       </c>
       <c r="N23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O23">
-        <v>86.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5149,40 +5149,40 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="F24">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="G24">
         <v>66.7</v>
       </c>
       <c r="H24">
-        <v>86.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="L24">
         <v>66.7</v>
       </c>
       <c r="M24">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="N24">
-        <v>120</v>
+        <v>84.8</v>
       </c>
       <c r="O24">
-        <v>76.7</v>
+        <v>84.5</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>84.8</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5190,7 +5190,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="C25">
         <v>95</v>
@@ -5199,58 +5199,58 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="F25">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G25">
         <v>83.3</v>
       </c>
       <c r="H25">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I25">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J25">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25">
-        <v>106.7</v>
+        <v>83.3</v>
       </c>
       <c r="M25">
-        <v>66.7</v>
+        <v>82</v>
       </c>
       <c r="N25">
-        <v>120</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O25">
-        <v>86.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5258,7 +5258,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="C26">
         <v>90</v>
@@ -5267,49 +5267,49 @@
         <v>100</v>
       </c>
       <c r="F26">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="G26">
         <v>83.3</v>
       </c>
       <c r="H26">
-        <v>83.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="J26">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="K26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M26">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="N26">
-        <v>120</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O26">
-        <v>63.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5317,7 +5317,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="C27">
         <v>90</v>
@@ -5326,49 +5326,49 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="G27">
         <v>86.7</v>
       </c>
       <c r="H27">
-        <v>96.7</v>
+        <v>93.5</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="J27">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="K27">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M27">
-        <v>53.3</v>
+        <v>72</v>
       </c>
       <c r="N27">
-        <v>120</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O27">
-        <v>70</v>
+        <v>86.2</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5376,7 +5376,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -5385,58 +5385,58 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F28">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>100</v>
       </c>
       <c r="H28">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="J28">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>106.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M28">
-        <v>73.3</v>
+        <v>94</v>
       </c>
       <c r="N28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>83.3</v>
+        <v>94.8</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5444,7 +5444,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -5453,58 +5453,58 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F29">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>100</v>
       </c>
       <c r="H29">
-        <v>103.3</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>100</v>
       </c>
       <c r="J29">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>86.7</v>
+        <v>98.3</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5512,7 +5512,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -5521,58 +5521,58 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F30">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>100</v>
       </c>
       <c r="H30">
-        <v>103.3</v>
+        <v>100</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J30">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>113.3</v>
+        <v>97.2</v>
       </c>
       <c r="M30">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="N30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>86.7</v>
+        <v>98.3</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5580,7 +5580,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -5589,58 +5589,58 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F31">
-        <v>73.3</v>
+        <v>88</v>
       </c>
       <c r="G31">
         <v>100</v>
       </c>
       <c r="H31">
-        <v>96.7</v>
+        <v>93.5</v>
       </c>
       <c r="I31">
         <v>100</v>
       </c>
       <c r="J31">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K31">
         <v>100</v>
       </c>
       <c r="L31">
-        <v>113.3</v>
+        <v>97.2</v>
       </c>
       <c r="M31">
-        <v>73.3</v>
+        <v>88</v>
       </c>
       <c r="N31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>80</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -5648,7 +5648,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -5657,58 +5657,58 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>93.3</v>
+        <v>77.8</v>
       </c>
       <c r="F32">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G32">
         <v>100</v>
       </c>
       <c r="H32">
-        <v>96.7</v>
+        <v>93.5</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J32">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>113.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="M32">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="N32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O32">
-        <v>80</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -5716,7 +5716,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -5725,58 +5725,58 @@
         <v>100</v>
       </c>
       <c r="E33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F33">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>100</v>
       </c>
       <c r="H33">
-        <v>103.3</v>
+        <v>100</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="J33">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K33">
         <v>100</v>
       </c>
       <c r="L33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M33">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="N33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O33">
-        <v>86.7</v>
+        <v>98.3</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -5784,7 +5784,7 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -5793,58 +5793,58 @@
         <v>100</v>
       </c>
       <c r="E34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F34">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G34">
         <v>100</v>
       </c>
       <c r="H34">
-        <v>96.7</v>
+        <v>93.5</v>
       </c>
       <c r="I34">
         <v>100</v>
       </c>
       <c r="J34">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="L34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M34">
-        <v>76.7</v>
+        <v>94</v>
       </c>
       <c r="N34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O34">
-        <v>83.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -5852,7 +5852,7 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -5861,58 +5861,58 @@
         <v>100</v>
       </c>
       <c r="E35">
-        <v>106.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F35">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G35">
         <v>100</v>
       </c>
       <c r="H35">
-        <v>103.3</v>
+        <v>100</v>
       </c>
       <c r="I35">
         <v>100</v>
       </c>
       <c r="J35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K35">
         <v>100</v>
       </c>
       <c r="L35">
-        <v>106.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M35">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="N35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O35">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -5920,67 +5920,67 @@
         <v>45</v>
       </c>
       <c r="B36">
+        <v>66.7</v>
+      </c>
+      <c r="C36">
+        <v>100</v>
+      </c>
+      <c r="D36">
+        <v>100</v>
+      </c>
+      <c r="E36">
+        <v>100</v>
+      </c>
+      <c r="F36">
         <v>80</v>
       </c>
-      <c r="C36">
-        <v>100</v>
-      </c>
-      <c r="D36">
-        <v>100</v>
-      </c>
-      <c r="E36">
-        <v>120</v>
-      </c>
-      <c r="F36">
-        <v>66.7</v>
-      </c>
       <c r="G36">
         <v>100</v>
       </c>
       <c r="H36">
-        <v>96.7</v>
+        <v>93.5</v>
       </c>
       <c r="I36">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="J36">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="K36">
         <v>100</v>
       </c>
       <c r="L36">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="M36">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="N36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O36">
-        <v>73.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4AEV - Estadisticos 20222.xlsx
+++ b/grupos/4AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="87">
   <si>
     <t>Materia</t>
   </si>
@@ -194,27 +194,27 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Barañon Samaniego Graciela de los Ángeles</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Barañon Samaniego Graciela de los Ángeles</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -227,6 +227,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -236,16 +245,10 @@
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>PERALTA</t>
+    <t>MARCELINO</t>
   </si>
   <si>
     <t>FLORES</t>
@@ -254,13 +257,16 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>GALLARDO</t>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
   </si>
   <si>
     <t>DULIAM</t>
@@ -272,19 +278,7 @@
     <t>OMAR</t>
   </si>
   <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
     <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
   </si>
 </sst>
 </file>
@@ -838,13 +832,13 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -859,7 +853,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>5</v>
@@ -927,13 +921,13 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -948,13 +942,13 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB5">
         <v>6</v>
@@ -1016,13 +1010,13 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1105,13 +1099,13 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1126,7 +1120,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -1194,13 +1188,13 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1283,13 +1277,13 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1304,13 +1298,13 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB9">
         <v>5</v>
@@ -1372,13 +1366,13 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1393,7 +1387,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z10">
         <v>8</v>
@@ -1461,13 +1455,13 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1482,13 +1476,13 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z11">
         <v>8</v>
       </c>
       <c r="AA11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB11">
         <v>8</v>
@@ -1550,13 +1544,13 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1571,7 +1565,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1639,13 +1633,13 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1660,7 +1654,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z13">
         <v>8</v>
@@ -1728,13 +1722,13 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1749,13 +1743,13 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>5</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB14">
         <v>7</v>
@@ -1817,13 +1811,13 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1906,13 +1900,13 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -1927,13 +1921,13 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB16">
         <v>5</v>
@@ -1995,13 +1989,13 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2016,7 +2010,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z17">
         <v>7</v>
@@ -2084,13 +2078,13 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2173,13 +2167,13 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2262,13 +2256,13 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2283,7 +2277,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>8</v>
@@ -2351,13 +2345,13 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2440,13 +2434,13 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2529,13 +2523,13 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2597,7 +2591,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2671,13 +2665,13 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2698,7 +2692,7 @@
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB25">
         <v>7</v>
@@ -2754,10 +2748,10 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2772,7 +2766,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA26">
         <v>8</v>
@@ -2831,10 +2825,10 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -2849,10 +2843,10 @@
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB27">
         <v>7</v>
@@ -2914,13 +2908,13 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -2935,13 +2929,13 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>8</v>
       </c>
       <c r="AA28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>8</v>
@@ -3003,13 +2997,13 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3092,13 +3086,13 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3113,13 +3107,13 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z30">
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB30">
         <v>9</v>
@@ -3181,13 +3175,13 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3208,7 +3202,7 @@
         <v>8</v>
       </c>
       <c r="AA31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB31">
         <v>8</v>
@@ -3270,13 +3264,13 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3291,7 +3285,7 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z32">
         <v>5</v>
@@ -3359,13 +3353,13 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3448,13 +3442,13 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S34">
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3469,7 +3463,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z34">
         <v>7</v>
@@ -3537,13 +3531,13 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3626,13 +3620,13 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U36">
         <v>-1</v>
@@ -3647,7 +3641,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z36">
         <v>5</v>
@@ -3837,13 +3831,13 @@
         <v>90</v>
       </c>
       <c r="R4">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S4">
         <v>47.2</v>
       </c>
       <c r="T4">
-        <v>70</v>
+        <v>93.8</v>
       </c>
       <c r="U4">
         <v>89.40000000000001</v>
@@ -3911,7 +3905,7 @@
         <v>72.2</v>
       </c>
       <c r="T5">
-        <v>76</v>
+        <v>93.8</v>
       </c>
       <c r="U5">
         <v>100</v>
@@ -3979,7 +3973,7 @@
         <v>75</v>
       </c>
       <c r="T6">
-        <v>80</v>
+        <v>93.8</v>
       </c>
       <c r="U6">
         <v>90.90000000000001</v>
@@ -4047,7 +4041,7 @@
         <v>25</v>
       </c>
       <c r="T7">
-        <v>28</v>
+        <v>34.4</v>
       </c>
       <c r="U7">
         <v>89.40000000000001</v>
@@ -4115,7 +4109,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="T8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -4162,7 +4156,7 @@
         <v>77.8</v>
       </c>
       <c r="M9">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="N9">
         <v>92.40000000000001</v>
@@ -4183,7 +4177,7 @@
         <v>77.8</v>
       </c>
       <c r="T9">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="U9">
         <v>92.40000000000001</v>
@@ -4251,7 +4245,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="T10">
-        <v>76</v>
+        <v>93.8</v>
       </c>
       <c r="U10">
         <v>97</v>
@@ -4319,7 +4313,7 @@
         <v>97.2</v>
       </c>
       <c r="T11">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -4387,7 +4381,7 @@
         <v>44.4</v>
       </c>
       <c r="T12">
-        <v>64</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="U12">
         <v>84.8</v>
@@ -4455,7 +4449,7 @@
         <v>97.2</v>
       </c>
       <c r="T13">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -4523,7 +4517,7 @@
         <v>91.7</v>
       </c>
       <c r="T14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -4591,7 +4585,7 @@
         <v>72.2</v>
       </c>
       <c r="T15">
-        <v>80</v>
+        <v>93.8</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -4659,7 +4653,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="T16">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -4727,7 +4721,7 @@
         <v>97.2</v>
       </c>
       <c r="T17">
-        <v>86</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U17">
         <v>93.90000000000001</v>
@@ -4789,13 +4783,13 @@
         <v>80</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S18">
         <v>41.7</v>
       </c>
       <c r="T18">
-        <v>52</v>
+        <v>46.9</v>
       </c>
       <c r="U18">
         <v>93.90000000000001</v>
@@ -4931,7 +4925,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="T20">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="U20">
         <v>97</v>
@@ -4993,13 +4987,13 @@
         <v>0</v>
       </c>
       <c r="R21">
-        <v>75</v>
+        <v>46.9</v>
       </c>
       <c r="S21">
         <v>0</v>
       </c>
       <c r="T21">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="U21">
         <v>42.4</v>
@@ -5067,7 +5061,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="T22">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -5135,7 +5129,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="T23">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -5176,7 +5170,7 @@
         <v>66.7</v>
       </c>
       <c r="T24">
-        <v>50</v>
+        <v>48.4</v>
       </c>
       <c r="U24">
         <v>84.8</v>
@@ -5244,7 +5238,7 @@
         <v>83.3</v>
       </c>
       <c r="T25">
-        <v>82</v>
+        <v>95.3</v>
       </c>
       <c r="U25">
         <v>92.40000000000001</v>
@@ -5300,10 +5294,10 @@
         <v>87.5</v>
       </c>
       <c r="R26">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T26">
-        <v>76</v>
+        <v>93.8</v>
       </c>
       <c r="U26">
         <v>92.40000000000001</v>
@@ -5359,10 +5353,10 @@
         <v>87.5</v>
       </c>
       <c r="R27">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T27">
-        <v>72</v>
+        <v>93.8</v>
       </c>
       <c r="U27">
         <v>93.90000000000001</v>
@@ -5430,7 +5424,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="T28">
-        <v>94</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -5566,7 +5560,7 @@
         <v>97.2</v>
       </c>
       <c r="T30">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="U30">
         <v>100</v>
@@ -5634,7 +5628,7 @@
         <v>97.2</v>
       </c>
       <c r="T31">
-        <v>88</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -5702,7 +5696,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="T32">
-        <v>84</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -5770,7 +5764,7 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="U33">
         <v>100</v>
@@ -5838,7 +5832,7 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>94</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U34">
         <v>100</v>
@@ -5906,7 +5900,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="T35">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -5974,7 +5968,7 @@
         <v>91.7</v>
       </c>
       <c r="T36">
-        <v>76</v>
+        <v>93.8</v>
       </c>
       <c r="U36">
         <v>100</v>
@@ -6037,28 +6031,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2">
         <v>18</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2">
-        <v>56.2</v>
+        <v>58.1</v>
       </c>
       <c r="G2" s="2">
-        <v>43.8</v>
+        <v>41.9</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6069,28 +6063,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3">
         <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>58.1</v>
+        <v>60.6</v>
       </c>
       <c r="G3" s="2">
-        <v>41.9</v>
+        <v>39.4</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6101,7 +6095,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -6110,16 +6104,16 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2">
-        <v>60.6</v>
+        <v>66.7</v>
       </c>
       <c r="G4" s="2">
-        <v>39.4</v>
+        <v>33.3</v>
       </c>
       <c r="H4">
         <v>6.7</v>
@@ -6133,28 +6127,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="G5" s="2">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6165,28 +6159,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>72.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>27.3</v>
+        <v>21.9</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6197,28 +6191,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
       </c>
       <c r="C7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2">
-        <v>75</v>
+        <v>78.8</v>
       </c>
       <c r="G7" s="2">
-        <v>25</v>
+        <v>21.2</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6229,7 +6223,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>64</v>
@@ -6238,19 +6232,19 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>78.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="G8" s="2">
-        <v>21.9</v>
+        <v>6.2</v>
       </c>
       <c r="H8">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6300,7 +6294,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6332,7 +6326,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920078</v>
+        <v>21330051920003</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
@@ -6341,10 +6335,10 @@
         <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>58</v>
@@ -6355,7 +6349,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920078</v>
+        <v>21330051920003</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
@@ -6364,13 +6358,13 @@
         <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6378,22 +6372,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920012</v>
+        <v>20330051920366</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6401,19 +6395,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920012</v>
+        <v>20330051920366</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>60</v>
@@ -6424,19 +6418,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920013</v>
+        <v>21330051920023</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>58</v>
@@ -6447,22 +6441,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920013</v>
+        <v>21330051920023</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6470,22 +6464,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920366</v>
+        <v>20330051920078</v>
       </c>
       <c r="B8" t="s">
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6493,22 +6487,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920366</v>
+        <v>21330051920012</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
         <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6516,10 +6510,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920018</v>
+        <v>21330051920013</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
         <v>78</v>
@@ -6528,10 +6522,10 @@
         <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6542,7 +6536,7 @@
         <v>21330051920379</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
         <v>79</v>
@@ -6554,55 +6548,9 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920367</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920018</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEV - Estadisticos 20222.xlsx
+++ b/grupos/4AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="85">
   <si>
     <t>Materia</t>
   </si>
@@ -194,24 +194,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
     <t>Barañon Samaniego Graciela de los Ángeles</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
@@ -227,7 +227,16 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BAEZ</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>NAJERA</t>
@@ -236,49 +245,34 @@
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
   </si>
   <si>
     <t>ELI ANTONIO</t>
   </si>
   <si>
     <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
   </si>
 </sst>
 </file>
@@ -829,13 +823,13 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>6</v>
@@ -844,13 +838,13 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>5</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -918,13 +912,13 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -933,19 +927,19 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>6</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>6</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>6</v>
@@ -954,7 +948,7 @@
         <v>6</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1007,13 +1001,13 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1022,19 +1016,19 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>6</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>6</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -1043,7 +1037,7 @@
         <v>5</v>
       </c>
       <c r="AC6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1096,13 +1090,13 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -1111,7 +1105,7 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1185,13 +1179,13 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1200,7 +1194,7 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1212,7 +1206,7 @@
         <v>7</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -1274,13 +1268,13 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1289,19 +1283,19 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>6</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA9">
         <v>7</v>
@@ -1310,7 +1304,7 @@
         <v>5</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1363,13 +1357,13 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1378,13 +1372,13 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>7</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1452,13 +1446,13 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1467,7 +1461,7 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1541,13 +1535,13 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T12">
         <v>3</v>
@@ -1556,13 +1550,13 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>5</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1630,13 +1624,13 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1645,7 +1639,7 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1657,7 +1651,7 @@
         <v>8</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA13">
         <v>10</v>
@@ -1719,13 +1713,13 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
         <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -1734,7 +1728,7 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1746,7 +1740,7 @@
         <v>6</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1808,13 +1802,13 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>7</v>
@@ -1823,19 +1817,19 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>5</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>6</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>6</v>
@@ -1844,7 +1838,7 @@
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1897,13 +1891,13 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -1912,7 +1906,7 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1924,7 +1918,7 @@
         <v>6</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -1986,13 +1980,13 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -2001,7 +1995,7 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2013,7 +2007,7 @@
         <v>7</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -2022,7 +2016,7 @@
         <v>8</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2075,13 +2069,13 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T18">
         <v>3</v>
@@ -2090,7 +2084,7 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2164,13 +2158,13 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2179,7 +2173,7 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2200,7 +2194,7 @@
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2253,13 +2247,13 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>8</v>
@@ -2268,7 +2262,7 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2280,7 +2274,7 @@
         <v>7</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA20">
         <v>7</v>
@@ -2289,7 +2283,7 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2342,13 +2336,13 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -2357,7 +2351,7 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2431,13 +2425,13 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2446,19 +2440,19 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>7</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2520,13 +2514,13 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2535,7 +2529,7 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2547,7 +2541,7 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>10</v>
@@ -2556,7 +2550,7 @@
         <v>8</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2588,7 +2582,7 @@
         <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>4</v>
@@ -2597,7 +2591,7 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z24">
         <v>5</v>
@@ -2609,7 +2603,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2662,13 +2656,13 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
         <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>6</v>
@@ -2677,7 +2671,7 @@
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2689,7 +2683,7 @@
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -2745,7 +2739,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
         <v>8</v>
@@ -2757,13 +2751,13 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>6</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2775,7 +2769,7 @@
         <v>5</v>
       </c>
       <c r="AC26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2822,7 +2816,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
         <v>9</v>
@@ -2834,13 +2828,13 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>6</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2905,13 +2899,13 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>7</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -2920,7 +2914,7 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2941,7 +2935,7 @@
         <v>8</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -2994,13 +2988,13 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -3009,7 +3003,7 @@
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -3030,7 +3024,7 @@
         <v>8</v>
       </c>
       <c r="AC29">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3083,13 +3077,13 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>8</v>
@@ -3098,7 +3092,7 @@
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3110,7 +3104,7 @@
         <v>8</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA30">
         <v>9</v>
@@ -3119,7 +3113,7 @@
         <v>9</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3172,13 +3166,13 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
         <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>6</v>
@@ -3187,7 +3181,7 @@
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -3261,13 +3255,13 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
         <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>7</v>
@@ -3276,19 +3270,19 @@
         <v>-1</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>6</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>6</v>
       </c>
       <c r="Z32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA32">
         <v>8</v>
@@ -3350,13 +3344,13 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3365,13 +3359,13 @@
         <v>-1</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>9</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3386,7 +3380,7 @@
         <v>9</v>
       </c>
       <c r="AC33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3439,13 +3433,13 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
         <v>5</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>8</v>
@@ -3454,7 +3448,7 @@
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>6</v>
@@ -3466,7 +3460,7 @@
         <v>6</v>
       </c>
       <c r="Z34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA34">
         <v>7</v>
@@ -3528,13 +3522,13 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>9</v>
@@ -3543,7 +3537,7 @@
         <v>-1</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -3617,13 +3611,13 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
         <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
         <v>8</v>
@@ -3632,19 +3626,19 @@
         <v>-1</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>5</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>6</v>
       </c>
       <c r="Z36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA36">
         <v>5</v>
@@ -3828,13 +3822,13 @@
         <v>90.90000000000001</v>
       </c>
       <c r="Q4">
-        <v>90</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="R4">
         <v>84.40000000000001</v>
       </c>
       <c r="S4">
-        <v>47.2</v>
+        <v>64.8</v>
       </c>
       <c r="T4">
         <v>93.8</v>
@@ -3843,7 +3837,7 @@
         <v>89.40000000000001</v>
       </c>
       <c r="V4">
-        <v>82.8</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3896,13 +3890,13 @@
         <v>97.7</v>
       </c>
       <c r="Q5">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>72.2</v>
+        <v>81.5</v>
       </c>
       <c r="T5">
         <v>93.8</v>
@@ -3911,7 +3905,7 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>82.8</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3964,13 +3958,13 @@
         <v>97.7</v>
       </c>
       <c r="Q6">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="R6">
         <v>100</v>
       </c>
       <c r="S6">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="T6">
         <v>93.8</v>
@@ -3979,7 +3973,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V6">
-        <v>84.5</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4032,13 +4026,13 @@
         <v>90.90000000000001</v>
       </c>
       <c r="Q7">
-        <v>42.5</v>
+        <v>60.3</v>
       </c>
       <c r="R7">
         <v>100</v>
       </c>
       <c r="S7">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7">
         <v>34.4</v>
@@ -4047,7 +4041,7 @@
         <v>89.40000000000001</v>
       </c>
       <c r="V7">
-        <v>67.2</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4100,13 +4094,13 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>97.5</v>
+        <v>95.2</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>94.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -4115,7 +4109,7 @@
         <v>100</v>
       </c>
       <c r="V8">
-        <v>94.8</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4168,13 +4162,13 @@
         <v>97.7</v>
       </c>
       <c r="Q9">
-        <v>92.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R9">
         <v>100</v>
       </c>
       <c r="S9">
-        <v>77.8</v>
+        <v>85.2</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -4183,7 +4177,7 @@
         <v>92.40000000000001</v>
       </c>
       <c r="V9">
-        <v>86.2</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4236,13 +4230,13 @@
         <v>97.7</v>
       </c>
       <c r="Q10">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="R10">
         <v>100</v>
       </c>
       <c r="S10">
-        <v>86.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="T10">
         <v>93.8</v>
@@ -4251,7 +4245,7 @@
         <v>97</v>
       </c>
       <c r="V10">
-        <v>91.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4304,13 +4298,13 @@
         <v>97.7</v>
       </c>
       <c r="Q11">
-        <v>92.5</v>
+        <v>93.7</v>
       </c>
       <c r="R11">
         <v>100</v>
       </c>
       <c r="S11">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -4319,7 +4313,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>89.7</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4372,13 +4366,13 @@
         <v>84.09999999999999</v>
       </c>
       <c r="Q12">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="R12">
         <v>100</v>
       </c>
       <c r="S12">
-        <v>44.4</v>
+        <v>29.6</v>
       </c>
       <c r="T12">
         <v>78.09999999999999</v>
@@ -4387,7 +4381,7 @@
         <v>84.8</v>
       </c>
       <c r="V12">
-        <v>82.8</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4440,13 +4434,13 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -4455,7 +4449,7 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>89.7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4508,13 +4502,13 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>90</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>91.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T14">
         <v>100</v>
@@ -4523,7 +4517,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>87.90000000000001</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4576,13 +4570,13 @@
         <v>95.5</v>
       </c>
       <c r="Q15">
-        <v>87.5</v>
+        <v>87.3</v>
       </c>
       <c r="R15">
         <v>100</v>
       </c>
       <c r="S15">
-        <v>72.2</v>
+        <v>81.5</v>
       </c>
       <c r="T15">
         <v>93.8</v>
@@ -4591,7 +4585,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>91.40000000000001</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4644,13 +4638,13 @@
         <v>95.5</v>
       </c>
       <c r="Q16">
-        <v>90</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R16">
         <v>100</v>
       </c>
       <c r="S16">
-        <v>86.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -4659,7 +4653,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>89.7</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4712,13 +4706,13 @@
         <v>97.7</v>
       </c>
       <c r="Q17">
-        <v>90</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="R17">
         <v>100</v>
       </c>
       <c r="S17">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="T17">
         <v>98.40000000000001</v>
@@ -4727,7 +4721,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="V17">
-        <v>91.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4780,13 +4774,13 @@
         <v>86.40000000000001</v>
       </c>
       <c r="Q18">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="R18">
         <v>65.59999999999999</v>
       </c>
       <c r="S18">
-        <v>41.7</v>
+        <v>27.8</v>
       </c>
       <c r="T18">
         <v>46.9</v>
@@ -4795,7 +4789,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="V18">
-        <v>82.8</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4863,7 +4857,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>98.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4916,13 +4910,13 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R20">
         <v>100</v>
       </c>
       <c r="S20">
-        <v>94.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -4999,7 +4993,7 @@
         <v>42.4</v>
       </c>
       <c r="V21">
-        <v>41.4</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5052,13 +5046,13 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="R22">
         <v>100</v>
       </c>
       <c r="S22">
-        <v>86.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="T22">
         <v>100</v>
@@ -5067,7 +5061,7 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5120,13 +5114,13 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5167,7 +5161,7 @@
         <v>84.5</v>
       </c>
       <c r="S24">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="T24">
         <v>48.4</v>
@@ -5176,7 +5170,7 @@
         <v>84.8</v>
       </c>
       <c r="V24">
-        <v>84.5</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5229,13 +5223,13 @@
         <v>90.90000000000001</v>
       </c>
       <c r="Q25">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="R25">
         <v>100</v>
       </c>
       <c r="S25">
-        <v>83.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T25">
         <v>95.3</v>
@@ -5291,7 +5285,7 @@
         <v>93.2</v>
       </c>
       <c r="Q26">
-        <v>87.5</v>
+        <v>90.5</v>
       </c>
       <c r="R26">
         <v>93.8</v>
@@ -5303,7 +5297,7 @@
         <v>92.40000000000001</v>
       </c>
       <c r="V26">
-        <v>75.90000000000001</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5350,7 +5344,7 @@
         <v>93.2</v>
       </c>
       <c r="Q27">
-        <v>87.5</v>
+        <v>90.5</v>
       </c>
       <c r="R27">
         <v>93.8</v>
@@ -5362,7 +5356,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="V27">
-        <v>86.2</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5415,13 +5409,13 @@
         <v>93.2</v>
       </c>
       <c r="Q28">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="R28">
         <v>100</v>
       </c>
       <c r="S28">
-        <v>94.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="T28">
         <v>98.40000000000001</v>
@@ -5430,7 +5424,7 @@
         <v>100</v>
       </c>
       <c r="V28">
-        <v>94.8</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5483,7 +5477,7 @@
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -5498,7 +5492,7 @@
         <v>100</v>
       </c>
       <c r="V29">
-        <v>98.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5551,13 +5545,13 @@
         <v>95.5</v>
       </c>
       <c r="Q30">
-        <v>92.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R30">
         <v>100</v>
       </c>
       <c r="S30">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="T30">
         <v>100</v>
@@ -5566,7 +5560,7 @@
         <v>100</v>
       </c>
       <c r="V30">
-        <v>98.3</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5619,13 +5613,13 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="R31">
         <v>100</v>
       </c>
       <c r="S31">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="T31">
         <v>96.90000000000001</v>
@@ -5634,7 +5628,7 @@
         <v>100</v>
       </c>
       <c r="V31">
-        <v>91.40000000000001</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -5687,13 +5681,13 @@
         <v>95.5</v>
       </c>
       <c r="Q32">
-        <v>92.5</v>
+        <v>90.5</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="S32">
-        <v>86.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="T32">
         <v>96.90000000000001</v>
@@ -5702,7 +5696,7 @@
         <v>100</v>
       </c>
       <c r="V32">
-        <v>91.40000000000001</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -5755,7 +5749,7 @@
         <v>97.7</v>
       </c>
       <c r="Q33">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -5770,7 +5764,7 @@
         <v>100</v>
       </c>
       <c r="V33">
-        <v>98.3</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -5823,7 +5817,7 @@
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>92.5</v>
+        <v>93.7</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -5838,7 +5832,7 @@
         <v>100</v>
       </c>
       <c r="V34">
-        <v>93.09999999999999</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -5891,13 +5885,13 @@
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="R35">
         <v>100</v>
       </c>
       <c r="S35">
-        <v>88.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="T35">
         <v>100</v>
@@ -5906,7 +5900,7 @@
         <v>100</v>
       </c>
       <c r="V35">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -5959,13 +5953,13 @@
         <v>81.8</v>
       </c>
       <c r="Q36">
-        <v>92.5</v>
+        <v>90.5</v>
       </c>
       <c r="R36">
         <v>100</v>
       </c>
       <c r="S36">
-        <v>91.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T36">
         <v>93.8</v>
@@ -5974,7 +5968,7 @@
         <v>100</v>
       </c>
       <c r="V36">
-        <v>87.90000000000001</v>
+        <v>90.8</v>
       </c>
     </row>
   </sheetData>
@@ -6031,28 +6025,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>13</v>
       </c>
       <c r="F2" s="2">
-        <v>58.1</v>
+        <v>60.6</v>
       </c>
       <c r="G2" s="2">
-        <v>41.9</v>
+        <v>39.4</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6063,28 +6057,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>60.6</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>39.4</v>
+        <v>21.9</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6095,7 +6089,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -6104,19 +6098,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>66.7</v>
+        <v>78.8</v>
       </c>
       <c r="G4" s="2">
-        <v>33.3</v>
+        <v>21.2</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6127,28 +6121,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>75</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>25</v>
+        <v>19.4</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6159,25 +6153,25 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>78.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="G6" s="2">
-        <v>21.9</v>
+        <v>15.2</v>
       </c>
       <c r="H6">
         <v>6.8</v>
@@ -6191,28 +6185,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>78.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>21.2</v>
+        <v>9.4</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6294,7 +6288,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6326,22 +6320,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920003</v>
+        <v>21330051920195</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6349,22 +6343,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920003</v>
+        <v>21330051920195</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6372,22 +6366,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920366</v>
+        <v>21330051920005</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6395,22 +6389,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920366</v>
+        <v>20330051920049</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
         <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6418,19 +6412,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920023</v>
+        <v>21330051920012</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
         <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>58</v>
@@ -6441,22 +6435,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920023</v>
+        <v>20330051920366</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6464,93 +6458,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920078</v>
+        <v>21330051920023</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>58</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920012</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920013</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920379</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEV - Estadisticos 20222.xlsx
+++ b/grupos/4AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="78">
   <si>
     <t>Materia</t>
   </si>
@@ -194,18 +194,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
@@ -227,49 +227,28 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
+    <t>ALEJANDRO</t>
   </si>
   <si>
     <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
   </si>
   <si>
     <t>NEMESIO NAHIM</t>
@@ -835,7 +814,7 @@
         <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -856,7 +835,7 @@
         <v>5</v>
       </c>
       <c r="AB4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC4">
         <v>5</v>
@@ -909,7 +888,7 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -924,7 +903,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -998,7 +977,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -1013,7 +992,7 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1034,7 +1013,7 @@
         <v>6</v>
       </c>
       <c r="AB6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC6">
         <v>6</v>
@@ -1087,7 +1066,7 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -1102,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -1176,7 +1155,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1191,7 +1170,7 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1212,7 +1191,7 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC8">
         <v>8</v>
@@ -1265,7 +1244,7 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -1280,7 +1259,7 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1354,7 +1333,7 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1369,7 +1348,7 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1443,7 +1422,7 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -1458,7 +1437,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1532,7 +1511,7 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -1547,7 +1526,7 @@
         <v>3</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -1568,7 +1547,7 @@
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1621,7 +1600,7 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1636,7 +1615,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1657,7 +1636,7 @@
         <v>10</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -1710,7 +1689,7 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>6</v>
@@ -1725,7 +1704,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -1799,7 +1778,7 @@
         <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>8</v>
@@ -1814,13 +1793,13 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>7</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1835,7 +1814,7 @@
         <v>6</v>
       </c>
       <c r="AB15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC15">
         <v>6</v>
@@ -1888,7 +1867,7 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -1903,7 +1882,7 @@
         <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1924,7 +1903,7 @@
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>7</v>
@@ -1977,7 +1956,7 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -1992,7 +1971,7 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -2013,7 +1992,7 @@
         <v>9</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC17">
         <v>6</v>
@@ -2066,7 +2045,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -2081,7 +2060,7 @@
         <v>3</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>6</v>
@@ -2155,7 +2134,7 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -2170,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2244,7 +2223,7 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>7</v>
@@ -2259,7 +2238,7 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2333,7 +2312,7 @@
         <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>5</v>
@@ -2348,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2422,7 +2401,7 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>8</v>
@@ -2437,13 +2416,13 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>8</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -2511,7 +2490,7 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>8</v>
@@ -2526,7 +2505,7 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2547,7 +2526,7 @@
         <v>10</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>8</v>
@@ -2588,7 +2567,7 @@
         <v>4</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>9</v>
@@ -2600,7 +2579,7 @@
         <v>5</v>
       </c>
       <c r="AB24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -2653,7 +2632,7 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>7</v>
@@ -2668,7 +2647,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>8</v>
@@ -2689,7 +2668,7 @@
         <v>7</v>
       </c>
       <c r="AB25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>8</v>
@@ -2736,7 +2715,7 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>5</v>
@@ -2748,13 +2727,13 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>7</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2766,7 +2745,7 @@
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC26">
         <v>6</v>
@@ -2813,7 +2792,7 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>5</v>
@@ -2825,7 +2804,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>7</v>
@@ -2896,7 +2875,7 @@
         <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>7</v>
@@ -2911,7 +2890,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>7</v>
@@ -2985,7 +2964,7 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>10</v>
@@ -3000,7 +2979,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -3021,7 +3000,7 @@
         <v>10</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC29">
         <v>8</v>
@@ -3074,7 +3053,7 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>9</v>
@@ -3089,7 +3068,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>7</v>
@@ -3163,7 +3142,7 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
         <v>6</v>
@@ -3178,7 +3157,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -3199,7 +3178,7 @@
         <v>7</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC31">
         <v>7</v>
@@ -3252,7 +3231,7 @@
         <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -3267,13 +3246,13 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>6</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -3341,7 +3320,7 @@
         <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -3356,13 +3335,13 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>8</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3430,7 +3409,7 @@
         <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>8</v>
@@ -3445,7 +3424,7 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3466,7 +3445,7 @@
         <v>7</v>
       </c>
       <c r="AB34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC34">
         <v>7</v>
@@ -3519,7 +3498,7 @@
         <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -3534,7 +3513,7 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>9</v>
@@ -3623,7 +3602,7 @@
         <v>8</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>7</v>
@@ -3819,7 +3798,7 @@
         <v>82.8</v>
       </c>
       <c r="P4">
-        <v>90.90000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="Q4">
         <v>88.90000000000001</v>
@@ -3834,7 +3813,7 @@
         <v>93.8</v>
       </c>
       <c r="U4">
-        <v>89.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="V4">
         <v>87.40000000000001</v>
@@ -3887,7 +3866,7 @@
         <v>82.8</v>
       </c>
       <c r="P5">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q5">
         <v>90.5</v>
@@ -3955,7 +3934,7 @@
         <v>84.5</v>
       </c>
       <c r="P6">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q6">
         <v>90.5</v>
@@ -3970,7 +3949,7 @@
         <v>93.8</v>
       </c>
       <c r="U6">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V6">
         <v>89.7</v>
@@ -4023,7 +4002,7 @@
         <v>67.2</v>
       </c>
       <c r="P7">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="Q7">
         <v>60.3</v>
@@ -4038,7 +4017,7 @@
         <v>34.4</v>
       </c>
       <c r="U7">
-        <v>89.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="V7">
         <v>73.59999999999999</v>
@@ -4091,7 +4070,7 @@
         <v>94.8</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q8">
         <v>95.2</v>
@@ -4159,7 +4138,7 @@
         <v>86.2</v>
       </c>
       <c r="P9">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="Q9">
         <v>92.09999999999999</v>
@@ -4174,7 +4153,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>92.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="V9">
         <v>88.5</v>
@@ -4227,7 +4206,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="P10">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q10">
         <v>90.5</v>
@@ -4242,7 +4221,7 @@
         <v>93.8</v>
       </c>
       <c r="U10">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V10">
         <v>93.09999999999999</v>
@@ -4295,7 +4274,7 @@
         <v>89.7</v>
       </c>
       <c r="P11">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q11">
         <v>93.7</v>
@@ -4363,7 +4342,7 @@
         <v>82.8</v>
       </c>
       <c r="P12">
-        <v>84.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="Q12">
         <v>82.5</v>
@@ -4378,7 +4357,7 @@
         <v>78.09999999999999</v>
       </c>
       <c r="U12">
-        <v>84.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V12">
         <v>83.90000000000001</v>
@@ -4431,7 +4410,7 @@
         <v>89.7</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q13">
         <v>98.40000000000001</v>
@@ -4567,7 +4546,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="P15">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q15">
         <v>87.3</v>
@@ -4635,7 +4614,7 @@
         <v>89.7</v>
       </c>
       <c r="P16">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q16">
         <v>92.09999999999999</v>
@@ -4703,7 +4682,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="P17">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="Q17">
         <v>88.90000000000001</v>
@@ -4718,7 +4697,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="U17">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V17">
         <v>93.09999999999999</v>
@@ -4771,7 +4750,7 @@
         <v>82.8</v>
       </c>
       <c r="P18">
-        <v>86.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="Q18">
         <v>82.5</v>
@@ -4786,7 +4765,7 @@
         <v>46.9</v>
       </c>
       <c r="U18">
-        <v>93.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V18">
         <v>78.2</v>
@@ -4922,7 +4901,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V20">
         <v>96.59999999999999</v>
@@ -4975,7 +4954,7 @@
         <v>41.4</v>
       </c>
       <c r="P21">
-        <v>59.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4990,7 +4969,7 @@
         <v>1.6</v>
       </c>
       <c r="U21">
-        <v>42.4</v>
+        <v>55.2</v>
       </c>
       <c r="V21">
         <v>27.6</v>
@@ -5043,7 +5022,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q22">
         <v>96.8</v>
@@ -5167,7 +5146,7 @@
         <v>48.4</v>
       </c>
       <c r="U24">
-        <v>84.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V24">
         <v>88.5</v>
@@ -5220,7 +5199,7 @@
         <v>96.59999999999999</v>
       </c>
       <c r="P25">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="Q25">
         <v>90.5</v>
@@ -5235,7 +5214,7 @@
         <v>95.3</v>
       </c>
       <c r="U25">
-        <v>92.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="V25">
         <v>96.59999999999999</v>
@@ -5282,7 +5261,7 @@
         <v>75.90000000000001</v>
       </c>
       <c r="P26">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="Q26">
         <v>90.5</v>
@@ -5294,7 +5273,7 @@
         <v>93.8</v>
       </c>
       <c r="U26">
-        <v>92.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="V26">
         <v>82.8</v>
@@ -5341,7 +5320,7 @@
         <v>86.2</v>
       </c>
       <c r="P27">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="Q27">
         <v>90.5</v>
@@ -5353,7 +5332,7 @@
         <v>93.8</v>
       </c>
       <c r="U27">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V27">
         <v>89.7</v>
@@ -5406,7 +5385,7 @@
         <v>94.8</v>
       </c>
       <c r="P28">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="Q28">
         <v>96.8</v>
@@ -5542,7 +5521,7 @@
         <v>98.3</v>
       </c>
       <c r="P30">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q30">
         <v>92.09999999999999</v>
@@ -5610,7 +5589,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q31">
         <v>96.8</v>
@@ -5678,7 +5657,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="P32">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q32">
         <v>90.5</v>
@@ -5746,7 +5725,7 @@
         <v>98.3</v>
       </c>
       <c r="P33">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q33">
         <v>96.8</v>
@@ -5814,7 +5793,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="P34">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q34">
         <v>93.7</v>
@@ -5950,7 +5929,7 @@
         <v>87.90000000000001</v>
       </c>
       <c r="P36">
-        <v>81.8</v>
+        <v>56.3</v>
       </c>
       <c r="Q36">
         <v>90.5</v>
@@ -6025,7 +6004,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -6034,19 +6013,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>60.6</v>
+        <v>78.8</v>
       </c>
       <c r="G2" s="2">
-        <v>39.4</v>
+        <v>21.2</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6057,28 +6036,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3">
         <v>25</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>78.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>21.9</v>
+        <v>19.4</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6089,28 +6068,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4">
         <v>26</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>78.8</v>
+        <v>81.2</v>
       </c>
       <c r="G4" s="2">
-        <v>21.2</v>
+        <v>18.8</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6121,28 +6100,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5">
         <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>80.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="G5" s="2">
-        <v>19.4</v>
+        <v>18.2</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6288,7 +6267,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6320,19 +6299,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920195</v>
+        <v>20330051920089</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" t="s">
         <v>75</v>
       </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>59</v>
@@ -6343,19 +6322,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920195</v>
+        <v>20330051920089</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
       </c>
       <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" t="s">
         <v>75</v>
       </c>
-      <c r="D3" t="s">
-        <v>79</v>
-      </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>58</v>
@@ -6366,22 +6345,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920005</v>
+        <v>20330051920049</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
       </c>
       <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" t="s">
         <v>76</v>
       </c>
-      <c r="D4" t="s">
-        <v>80</v>
-      </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6389,93 +6368,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920049</v>
+        <v>21330051920023</v>
       </c>
       <c r="B5" t="s">
         <v>71</v>
       </c>
       <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
         <v>77</v>
       </c>
-      <c r="D5" t="s">
-        <v>81</v>
-      </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920012</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920366</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920023</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEV - Estadisticos 20222.xlsx
+++ b/grupos/4AEV - Estadisticos 20222.xlsx
@@ -799,7 +799,7 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>8</v>
@@ -3587,7 +3587,7 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
         <v>7</v>
@@ -3798,7 +3798,7 @@
         <v>82.8</v>
       </c>
       <c r="P4">
-        <v>62.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q4">
         <v>88.90000000000001</v>
@@ -5929,7 +5929,7 @@
         <v>87.90000000000001</v>
       </c>
       <c r="P36">
-        <v>56.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q36">
         <v>90.5</v>
